--- a/Outputs/Tables/model_results.xlsx
+++ b/Outputs/Tables/model_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="148">
   <si>
     <t>model_id</t>
   </si>
@@ -419,6 +419,45 @@
   </si>
   <si>
     <t>H9_v2_no_re</t>
+  </si>
+  <si>
+    <t>SEL</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>selected_2025yes</t>
+  </si>
+  <si>
+    <t>Selected for 2025 (vs not selected)</t>
+  </si>
+  <si>
+    <t>selection for 2025</t>
+  </si>
+  <si>
+    <t>selected vs not selected</t>
+  </si>
+  <si>
+    <t>H1_sel</t>
+  </si>
+  <si>
+    <t>H2_sel</t>
+  </si>
+  <si>
+    <t>H3_sel</t>
+  </si>
+  <si>
+    <t>H4_sel</t>
+  </si>
+  <si>
+    <t>H5_sel</t>
+  </si>
+  <si>
+    <t>H6_sel</t>
+  </si>
+  <si>
+    <t>H10_H11_dens_sel</t>
   </si>
 </sst>
 </file>
@@ -761,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:39" s="1" customFormat="1">
@@ -2262,7 +2301,7 @@
         <v>43</v>
       </c>
       <c r="H14">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I14" t="s">
         <v>79</v>
@@ -2277,76 +2316,76 @@
         <v>82</v>
       </c>
       <c r="M14">
-        <v>-0.2395006559798704</v>
+        <v>-0.2405943634362787</v>
       </c>
       <c r="N14">
-        <v>0.05906521476119882</v>
+        <v>0.05909161563938495</v>
       </c>
       <c r="O14">
-        <v>-0.3552663496509436</v>
+        <v>-0.356411801877757</v>
       </c>
       <c r="P14">
-        <v>-0.1237349623087971</v>
+        <v>-0.1247769249948005</v>
       </c>
       <c r="Q14" t="s">
         <v>48</v>
       </c>
       <c r="R14">
-        <v>0.7870207570720159</v>
+        <v>0.7861604571456374</v>
       </c>
       <c r="S14">
-        <v>0.7009867107758859</v>
+        <v>0.7001842236801191</v>
       </c>
       <c r="T14">
-        <v>0.8836140008654735</v>
+        <v>0.8826937875449684</v>
       </c>
       <c r="U14">
-        <v>-4.054851183529487</v>
+        <v>-4.071548236293627</v>
       </c>
       <c r="V14">
-        <v>5.016623026380509E-05</v>
+        <v>4.67016885481096E-05</v>
       </c>
       <c r="W14" t="s">
         <v>83</v>
       </c>
       <c r="Y14">
-        <v>0.9506719515172445</v>
+        <v>0.949291554753827</v>
       </c>
       <c r="Z14">
-        <v>736.7349131309052</v>
+        <v>737.3943969359605</v>
       </c>
       <c r="AA14">
-        <v>0.02221573896424056</v>
+        <v>0.02238142697472956</v>
       </c>
       <c r="AD14">
-        <v>0.03980533125747573</v>
+        <v>0.06784264180268301</v>
       </c>
       <c r="AE14">
-        <v>0.03660659755046632</v>
+        <v>0.001469556216944566</v>
       </c>
       <c r="AF14">
-        <v>0.07620932279956938</v>
+        <v>0.1643337787564035</v>
       </c>
       <c r="AG14">
-        <v>0.04679908900884888</v>
+        <v>0.0001896768929190302</v>
       </c>
       <c r="AH14">
-        <v>0.0002779538572086349</v>
+        <v>1.115202326040787E-07</v>
       </c>
       <c r="AI14">
-        <v>-0.03804548423272073</v>
+        <v>-0.03863463149328259</v>
       </c>
       <c r="AJ14">
-        <v>0.9310189167649825</v>
+        <v>0.9345237712193043</v>
       </c>
       <c r="AK14">
-        <v>-0.03797980027138936</v>
+        <v>-0.07256750459461629</v>
       </c>
       <c r="AL14">
-        <v>0.7694699500385648</v>
+        <v>0.9298253846279774</v>
       </c>
       <c r="AM14">
-        <v>0.05782916707090745</v>
+        <v>0.04705701871042679</v>
       </c>
     </row>
     <row r="15" spans="1:39">
@@ -2372,7 +2411,7 @@
         <v>51</v>
       </c>
       <c r="H15">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I15" t="s">
         <v>79</v>
@@ -2387,34 +2426,34 @@
         <v>82</v>
       </c>
       <c r="M15">
-        <v>-0.255627384189141</v>
+        <v>-0.2564368026370864</v>
       </c>
       <c r="N15">
-        <v>0.06456600268507931</v>
+        <v>0.06469864403314127</v>
       </c>
       <c r="O15">
-        <v>-0.3821744240776129</v>
+        <v>-0.3832438147906205</v>
       </c>
       <c r="P15">
-        <v>-0.1290803443006692</v>
+        <v>-0.1296297904835523</v>
       </c>
       <c r="Q15" t="s">
         <v>48</v>
       </c>
       <c r="R15">
-        <v>0.7744304800782651</v>
+        <v>0.7738038953798549</v>
       </c>
       <c r="S15">
-        <v>0.6823760200166882</v>
+        <v>0.6816466834804681</v>
       </c>
       <c r="T15">
-        <v>0.8789033478339183</v>
+        <v>0.8784205703865862</v>
       </c>
       <c r="U15">
-        <v>-3.959163856495246</v>
+        <v>-3.963557605716266</v>
       </c>
       <c r="V15">
-        <v>7.521262299163614E-05</v>
+        <v>7.384103495028507E-05</v>
       </c>
       <c r="W15" t="s">
         <v>83</v>
@@ -2423,46 +2462,46 @@
         <v>84</v>
       </c>
       <c r="Z15">
-        <v>713.8587945361713</v>
+        <v>714.5562448815978</v>
       </c>
       <c r="AA15">
-        <v>0.02172407438118129</v>
+        <v>0.02176544459617957</v>
       </c>
       <c r="AB15">
-        <v>11.49346758029765</v>
+        <v>11.28571355337644</v>
       </c>
       <c r="AC15">
-        <v>0.9400970599578541</v>
+        <v>0.9425916142704889</v>
       </c>
       <c r="AD15">
-        <v>0.03980533125747573</v>
+        <v>0.06784264180268301</v>
       </c>
       <c r="AE15">
-        <v>0.03660659755046632</v>
+        <v>0.001469556216944566</v>
       </c>
       <c r="AF15">
-        <v>0.07620932279956938</v>
+        <v>0.1643337787564035</v>
       </c>
       <c r="AG15">
-        <v>0.04679908900884888</v>
+        <v>0.0001896768929190302</v>
       </c>
       <c r="AH15">
-        <v>0.0002779538572086349</v>
+        <v>1.115202326040787E-07</v>
       </c>
       <c r="AI15">
-        <v>-0.03804548423272073</v>
+        <v>-0.03863463149328259</v>
       </c>
       <c r="AJ15">
-        <v>0.9310189167649825</v>
+        <v>0.9345237712193043</v>
       </c>
       <c r="AK15">
-        <v>-0.03797980027138936</v>
+        <v>-0.07256750459461629</v>
       </c>
       <c r="AL15">
-        <v>0.7694699500385648</v>
+        <v>0.9298253846279774</v>
       </c>
       <c r="AM15">
-        <v>0.05782916707090745</v>
+        <v>0.04705701871042679</v>
       </c>
     </row>
     <row r="16" spans="1:39">
@@ -6550,6 +6589,3559 @@
       </c>
       <c r="AM53">
         <v>0.6420111310973664</v>
+      </c>
+    </row>
+    <row r="54" spans="1:39">
+      <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H54">
+        <v>374</v>
+      </c>
+      <c r="I54" t="s">
+        <v>137</v>
+      </c>
+      <c r="J54" t="s">
+        <v>138</v>
+      </c>
+      <c r="K54" t="s">
+        <v>139</v>
+      </c>
+      <c r="L54" t="s">
+        <v>140</v>
+      </c>
+      <c r="M54">
+        <v>0.8223070897627313</v>
+      </c>
+      <c r="N54">
+        <v>0.1646318583942316</v>
+      </c>
+      <c r="O54">
+        <v>0.4996345766021392</v>
+      </c>
+      <c r="P54">
+        <v>1.144979602923323</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>48</v>
+      </c>
+      <c r="R54">
+        <v>2.27574413166638</v>
+      </c>
+      <c r="S54">
+        <v>1.648118899438243</v>
+      </c>
+      <c r="T54">
+        <v>3.142377260875546</v>
+      </c>
+      <c r="U54">
+        <v>4.994823588722506</v>
+      </c>
+      <c r="V54">
+        <v>5.888957315982872E-07</v>
+      </c>
+      <c r="W54" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y54">
+        <v>1.441162896680988</v>
+      </c>
+      <c r="Z54">
+        <v>902.8581483301011</v>
+      </c>
+      <c r="AA54">
+        <v>0.02762861613804601</v>
+      </c>
+      <c r="AD54">
+        <v>0.06933851309196466</v>
+      </c>
+      <c r="AE54">
+        <v>0.001026783204042646</v>
+      </c>
+      <c r="AF54">
+        <v>0.1481086396905807</v>
+      </c>
+      <c r="AG54">
+        <v>0.0003840537702882179</v>
+      </c>
+      <c r="AH54">
+        <v>1.818928027286226E-05</v>
+      </c>
+      <c r="AI54">
+        <v>-0.02588526951029796</v>
+      </c>
+      <c r="AJ54">
+        <v>0.8396767899468884</v>
+      </c>
+      <c r="AK54">
+        <v>-0.01001602115510671</v>
+      </c>
+      <c r="AL54">
+        <v>0.5621150482536832</v>
+      </c>
+      <c r="AM54">
+        <v>0.453588621042432</v>
+      </c>
+    </row>
+    <row r="55" spans="1:39">
+      <c r="A55" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>130</v>
+      </c>
+      <c r="D55" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55">
+        <v>374</v>
+      </c>
+      <c r="I55" t="s">
+        <v>137</v>
+      </c>
+      <c r="J55" t="s">
+        <v>138</v>
+      </c>
+      <c r="K55" t="s">
+        <v>139</v>
+      </c>
+      <c r="L55" t="s">
+        <v>140</v>
+      </c>
+      <c r="M55">
+        <v>0.6307015043558203</v>
+      </c>
+      <c r="N55">
+        <v>0.1865424637767782</v>
+      </c>
+      <c r="O55">
+        <v>0.2650849937659674</v>
+      </c>
+      <c r="P55">
+        <v>0.9963180149456732</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>48</v>
+      </c>
+      <c r="R55">
+        <v>1.878928193366213</v>
+      </c>
+      <c r="S55">
+        <v>1.303541763993766</v>
+      </c>
+      <c r="T55">
+        <v>2.708291558691713</v>
+      </c>
+      <c r="U55">
+        <v>3.381007689008197</v>
+      </c>
+      <c r="V55">
+        <v>0.0007222052190865349</v>
+      </c>
+      <c r="W55" t="s">
+        <v>49</v>
+      </c>
+      <c r="X55" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z55">
+        <v>884.7353665926006</v>
+      </c>
+      <c r="AA55">
+        <v>0.01275054307681134</v>
+      </c>
+      <c r="AB55">
+        <v>8.526959216725968</v>
+      </c>
+      <c r="AC55">
+        <v>0.8167757341834979</v>
+      </c>
+      <c r="AD55">
+        <v>0.06933851309196466</v>
+      </c>
+      <c r="AE55">
+        <v>0.001026783204042646</v>
+      </c>
+      <c r="AF55">
+        <v>0.1481086396905807</v>
+      </c>
+      <c r="AG55">
+        <v>0.0003840537702882179</v>
+      </c>
+      <c r="AH55">
+        <v>1.818928027286226E-05</v>
+      </c>
+      <c r="AI55">
+        <v>-0.02588526951029796</v>
+      </c>
+      <c r="AJ55">
+        <v>0.8396767899468884</v>
+      </c>
+      <c r="AK55">
+        <v>-0.01001602115510671</v>
+      </c>
+      <c r="AL55">
+        <v>0.5621150482536832</v>
+      </c>
+      <c r="AM55">
+        <v>0.453588621042432</v>
+      </c>
+    </row>
+    <row r="56" spans="1:39">
+      <c r="A56" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56">
+        <v>374</v>
+      </c>
+      <c r="I56" t="s">
+        <v>44</v>
+      </c>
+      <c r="J56" t="s">
+        <v>45</v>
+      </c>
+      <c r="K56" t="s">
+        <v>46</v>
+      </c>
+      <c r="L56" t="s">
+        <v>47</v>
+      </c>
+      <c r="M56">
+        <v>0.1837367373277325</v>
+      </c>
+      <c r="N56">
+        <v>0.04502791738482565</v>
+      </c>
+      <c r="O56">
+        <v>0.09548364095462926</v>
+      </c>
+      <c r="P56">
+        <v>0.2719898337008357</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>48</v>
+      </c>
+      <c r="R56">
+        <v>1.201699418849147</v>
+      </c>
+      <c r="S56">
+        <v>1.100190823815116</v>
+      </c>
+      <c r="T56">
+        <v>1.312573657226804</v>
+      </c>
+      <c r="U56">
+        <v>4.080507116450638</v>
+      </c>
+      <c r="V56">
+        <v>4.493755339894761E-05</v>
+      </c>
+      <c r="W56" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y56">
+        <v>1.610342642196811</v>
+      </c>
+      <c r="Z56">
+        <v>887.9292941037833</v>
+      </c>
+      <c r="AA56">
+        <v>0.04598283797557035</v>
+      </c>
+      <c r="AD56">
+        <v>0.07635681243102253</v>
+      </c>
+      <c r="AE56">
+        <v>0.0003593902718281966</v>
+      </c>
+      <c r="AF56">
+        <v>0.1527717994070319</v>
+      </c>
+      <c r="AG56">
+        <v>0.0002628043229268925</v>
+      </c>
+      <c r="AH56">
+        <v>7.785932254478212E-08</v>
+      </c>
+      <c r="AI56">
+        <v>-0.0318942640787714</v>
+      </c>
+      <c r="AJ56">
+        <v>0.8944023106160381</v>
+      </c>
+      <c r="AK56">
+        <v>-0.005314827617772123</v>
+      </c>
+      <c r="AL56">
+        <v>0.5206033925842054</v>
+      </c>
+      <c r="AM56">
+        <v>0.4467207151138807</v>
+      </c>
+    </row>
+    <row r="57" spans="1:39">
+      <c r="A57" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" t="s">
+        <v>43</v>
+      </c>
+      <c r="H57">
+        <v>374</v>
+      </c>
+      <c r="I57" t="s">
+        <v>137</v>
+      </c>
+      <c r="J57" t="s">
+        <v>138</v>
+      </c>
+      <c r="K57" t="s">
+        <v>139</v>
+      </c>
+      <c r="L57" t="s">
+        <v>140</v>
+      </c>
+      <c r="M57">
+        <v>0.7086927576597999</v>
+      </c>
+      <c r="N57">
+        <v>0.165692071975388</v>
+      </c>
+      <c r="O57">
+        <v>0.3839422640642211</v>
+      </c>
+      <c r="P57">
+        <v>1.033443251255379</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>48</v>
+      </c>
+      <c r="R57">
+        <v>2.031334076322871</v>
+      </c>
+      <c r="S57">
+        <v>1.468060679377993</v>
+      </c>
+      <c r="T57">
+        <v>2.810727231914408</v>
+      </c>
+      <c r="U57">
+        <v>4.27716757483164</v>
+      </c>
+      <c r="V57">
+        <v>1.892863150243258E-05</v>
+      </c>
+      <c r="Y57">
+        <v>1.610342642196811</v>
+      </c>
+      <c r="Z57">
+        <v>887.9292941037833</v>
+      </c>
+      <c r="AA57">
+        <v>0.04598283797557035</v>
+      </c>
+      <c r="AD57">
+        <v>0.07635681243102253</v>
+      </c>
+      <c r="AE57">
+        <v>0.0003593902718281966</v>
+      </c>
+      <c r="AF57">
+        <v>0.1527717994070319</v>
+      </c>
+      <c r="AG57">
+        <v>0.0002628043229268925</v>
+      </c>
+      <c r="AH57">
+        <v>7.785932254478212E-08</v>
+      </c>
+      <c r="AI57">
+        <v>-0.0318942640787714</v>
+      </c>
+      <c r="AJ57">
+        <v>0.8944023106160381</v>
+      </c>
+      <c r="AK57">
+        <v>-0.005314827617772123</v>
+      </c>
+      <c r="AL57">
+        <v>0.5206033925842054</v>
+      </c>
+      <c r="AM57">
+        <v>0.4467207151138807</v>
+      </c>
+    </row>
+    <row r="58" spans="1:39">
+      <c r="A58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" t="s">
+        <v>50</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" t="s">
+        <v>51</v>
+      </c>
+      <c r="H58">
+        <v>374</v>
+      </c>
+      <c r="I58" t="s">
+        <v>44</v>
+      </c>
+      <c r="J58" t="s">
+        <v>45</v>
+      </c>
+      <c r="K58" t="s">
+        <v>46</v>
+      </c>
+      <c r="L58" t="s">
+        <v>47</v>
+      </c>
+      <c r="M58">
+        <v>0.2198727847003391</v>
+      </c>
+      <c r="N58">
+        <v>0.04659551187073627</v>
+      </c>
+      <c r="O58">
+        <v>0.1285472595924874</v>
+      </c>
+      <c r="P58">
+        <v>0.3111983098081907</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>48</v>
+      </c>
+      <c r="R58">
+        <v>1.245918220645357</v>
+      </c>
+      <c r="S58">
+        <v>1.137175162456077</v>
+      </c>
+      <c r="T58">
+        <v>1.365059899112992</v>
+      </c>
+      <c r="U58">
+        <v>4.718754572549881</v>
+      </c>
+      <c r="V58">
+        <v>2.372928895022983E-06</v>
+      </c>
+      <c r="W58" t="s">
+        <v>49</v>
+      </c>
+      <c r="X58" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z58">
+        <v>864.5299578564999</v>
+      </c>
+      <c r="AA58">
+        <v>0.03775498404133293</v>
+      </c>
+      <c r="AB58">
+        <v>10.28877032155407</v>
+      </c>
+      <c r="AC58">
+        <v>0.7720972877700959</v>
+      </c>
+      <c r="AD58">
+        <v>0.07635681243102253</v>
+      </c>
+      <c r="AE58">
+        <v>0.0003593902718281966</v>
+      </c>
+      <c r="AF58">
+        <v>0.1527717994070319</v>
+      </c>
+      <c r="AG58">
+        <v>0.0002628043229268925</v>
+      </c>
+      <c r="AH58">
+        <v>7.785932254478212E-08</v>
+      </c>
+      <c r="AI58">
+        <v>-0.0318942640787714</v>
+      </c>
+      <c r="AJ58">
+        <v>0.8944023106160381</v>
+      </c>
+      <c r="AK58">
+        <v>-0.005314827617772123</v>
+      </c>
+      <c r="AL58">
+        <v>0.5206033925842054</v>
+      </c>
+      <c r="AM58">
+        <v>0.4467207151138807</v>
+      </c>
+    </row>
+    <row r="59" spans="1:39">
+      <c r="A59" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>130</v>
+      </c>
+      <c r="D59" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" t="s">
+        <v>51</v>
+      </c>
+      <c r="H59">
+        <v>374</v>
+      </c>
+      <c r="I59" t="s">
+        <v>137</v>
+      </c>
+      <c r="J59" t="s">
+        <v>138</v>
+      </c>
+      <c r="K59" t="s">
+        <v>139</v>
+      </c>
+      <c r="L59" t="s">
+        <v>140</v>
+      </c>
+      <c r="M59">
+        <v>0.5214463342110527</v>
+      </c>
+      <c r="N59">
+        <v>0.1815211054056297</v>
+      </c>
+      <c r="O59">
+        <v>0.1656715051821195</v>
+      </c>
+      <c r="P59">
+        <v>0.8772211632399858</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>48</v>
+      </c>
+      <c r="R59">
+        <v>1.684462183983297</v>
+      </c>
+      <c r="S59">
+        <v>1.180185353267397</v>
+      </c>
+      <c r="T59">
+        <v>2.404209509476011</v>
+      </c>
+      <c r="U59">
+        <v>2.872648516798204</v>
+      </c>
+      <c r="V59">
+        <v>0.004070467038911334</v>
+      </c>
+      <c r="Z59">
+        <v>864.5299578564999</v>
+      </c>
+      <c r="AA59">
+        <v>0.03775498404133293</v>
+      </c>
+      <c r="AB59">
+        <v>10.28877032155407</v>
+      </c>
+      <c r="AC59">
+        <v>0.7720972877700959</v>
+      </c>
+      <c r="AD59">
+        <v>0.07635681243102253</v>
+      </c>
+      <c r="AE59">
+        <v>0.0003593902718281966</v>
+      </c>
+      <c r="AF59">
+        <v>0.1527717994070319</v>
+      </c>
+      <c r="AG59">
+        <v>0.0002628043229268925</v>
+      </c>
+      <c r="AH59">
+        <v>7.785932254478212E-08</v>
+      </c>
+      <c r="AI59">
+        <v>-0.0318942640787714</v>
+      </c>
+      <c r="AJ59">
+        <v>0.8944023106160381</v>
+      </c>
+      <c r="AK59">
+        <v>-0.005314827617772123</v>
+      </c>
+      <c r="AL59">
+        <v>0.5206033925842054</v>
+      </c>
+      <c r="AM59">
+        <v>0.4467207151138807</v>
+      </c>
+    </row>
+    <row r="60" spans="1:39">
+      <c r="A60" t="s">
+        <v>142</v>
+      </c>
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" t="s">
+        <v>43</v>
+      </c>
+      <c r="H60">
+        <v>374</v>
+      </c>
+      <c r="I60" t="s">
+        <v>54</v>
+      </c>
+      <c r="J60" t="s">
+        <v>55</v>
+      </c>
+      <c r="K60" t="s">
+        <v>56</v>
+      </c>
+      <c r="L60" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60">
+        <v>0.09198140757136483</v>
+      </c>
+      <c r="N60">
+        <v>0.02677808505973751</v>
+      </c>
+      <c r="O60">
+        <v>0.03949732527932922</v>
+      </c>
+      <c r="P60">
+        <v>0.1444654898634004</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>48</v>
+      </c>
+      <c r="R60">
+        <v>1.096344438185598</v>
+      </c>
+      <c r="S60">
+        <v>1.040287716402178</v>
+      </c>
+      <c r="T60">
+        <v>1.155421820510864</v>
+      </c>
+      <c r="U60">
+        <v>3.434950907287411</v>
+      </c>
+      <c r="V60">
+        <v>0.0005926611842661323</v>
+      </c>
+      <c r="W60" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y60">
+        <v>1.602155359344593</v>
+      </c>
+      <c r="Z60">
+        <v>892.7321552934454</v>
+      </c>
+      <c r="AA60">
+        <v>0.04077558776528434</v>
+      </c>
+      <c r="AD60">
+        <v>0.06640540107029785</v>
+      </c>
+      <c r="AE60">
+        <v>0.001556021051854706</v>
+      </c>
+      <c r="AF60">
+        <v>0.1347412409566866</v>
+      </c>
+      <c r="AG60">
+        <v>0.001084774980397903</v>
+      </c>
+      <c r="AH60">
+        <v>5.402772802143296E-05</v>
+      </c>
+      <c r="AI60">
+        <v>-0.03009702198996842</v>
+      </c>
+      <c r="AJ60">
+        <v>0.8796737195551009</v>
+      </c>
+      <c r="AK60">
+        <v>-0.02257141394089556</v>
+      </c>
+      <c r="AL60">
+        <v>0.6685256322146611</v>
+      </c>
+      <c r="AM60">
+        <v>0.4059848970405355</v>
+      </c>
+    </row>
+    <row r="61" spans="1:39">
+      <c r="A61" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G61" t="s">
+        <v>43</v>
+      </c>
+      <c r="H61">
+        <v>374</v>
+      </c>
+      <c r="I61" t="s">
+        <v>137</v>
+      </c>
+      <c r="J61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K61" t="s">
+        <v>139</v>
+      </c>
+      <c r="L61" t="s">
+        <v>140</v>
+      </c>
+      <c r="M61">
+        <v>0.7825504899640405</v>
+      </c>
+      <c r="N61">
+        <v>0.1639805784810339</v>
+      </c>
+      <c r="O61">
+        <v>0.4611544619771704</v>
+      </c>
+      <c r="P61">
+        <v>1.103946517950911</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>48</v>
+      </c>
+      <c r="R61">
+        <v>2.187043189891661</v>
+      </c>
+      <c r="S61">
+        <v>1.58590379419853</v>
+      </c>
+      <c r="T61">
+        <v>3.016045444842863</v>
+      </c>
+      <c r="U61">
+        <v>4.772214473280145</v>
+      </c>
+      <c r="V61">
+        <v>1.822113185456797E-06</v>
+      </c>
+      <c r="Y61">
+        <v>1.602155359344593</v>
+      </c>
+      <c r="Z61">
+        <v>892.7321552934454</v>
+      </c>
+      <c r="AA61">
+        <v>0.04077558776528434</v>
+      </c>
+      <c r="AD61">
+        <v>0.06640540107029785</v>
+      </c>
+      <c r="AE61">
+        <v>0.001556021051854706</v>
+      </c>
+      <c r="AF61">
+        <v>0.1347412409566866</v>
+      </c>
+      <c r="AG61">
+        <v>0.001084774980397903</v>
+      </c>
+      <c r="AH61">
+        <v>5.402772802143296E-05</v>
+      </c>
+      <c r="AI61">
+        <v>-0.03009702198996842</v>
+      </c>
+      <c r="AJ61">
+        <v>0.8796737195551009</v>
+      </c>
+      <c r="AK61">
+        <v>-0.02257141394089556</v>
+      </c>
+      <c r="AL61">
+        <v>0.6685256322146611</v>
+      </c>
+      <c r="AM61">
+        <v>0.4059848970405355</v>
+      </c>
+    </row>
+    <row r="62" spans="1:39">
+      <c r="A62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" t="s">
+        <v>50</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" t="s">
+        <v>51</v>
+      </c>
+      <c r="H62">
+        <v>374</v>
+      </c>
+      <c r="I62" t="s">
+        <v>54</v>
+      </c>
+      <c r="J62" t="s">
+        <v>55</v>
+      </c>
+      <c r="K62" t="s">
+        <v>56</v>
+      </c>
+      <c r="L62" t="s">
+        <v>57</v>
+      </c>
+      <c r="M62">
+        <v>0.08374235786997332</v>
+      </c>
+      <c r="N62">
+        <v>0.02488344765527489</v>
+      </c>
+      <c r="O62">
+        <v>0.03497169665444689</v>
+      </c>
+      <c r="P62">
+        <v>0.1325130190854998</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>48</v>
+      </c>
+      <c r="R62">
+        <v>1.08734871087896</v>
+      </c>
+      <c r="S62">
+        <v>1.035590397711946</v>
+      </c>
+      <c r="T62">
+        <v>1.141693879802664</v>
+      </c>
+      <c r="U62">
+        <v>3.365384050880156</v>
+      </c>
+      <c r="V62">
+        <v>0.0007643718563810635</v>
+      </c>
+      <c r="W62" t="s">
+        <v>49</v>
+      </c>
+      <c r="X62" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z62">
+        <v>876.3712098117336</v>
+      </c>
+      <c r="AA62">
+        <v>0.02442112070292457</v>
+      </c>
+      <c r="AB62">
+        <v>9.275946957166651</v>
+      </c>
+      <c r="AC62">
+        <v>0.7853691226453146</v>
+      </c>
+      <c r="AD62">
+        <v>0.06640540107029785</v>
+      </c>
+      <c r="AE62">
+        <v>0.001556021051854706</v>
+      </c>
+      <c r="AF62">
+        <v>0.1347412409566866</v>
+      </c>
+      <c r="AG62">
+        <v>0.001084774980397903</v>
+      </c>
+      <c r="AH62">
+        <v>5.402772802143296E-05</v>
+      </c>
+      <c r="AI62">
+        <v>-0.03009702198996842</v>
+      </c>
+      <c r="AJ62">
+        <v>0.8796737195551009</v>
+      </c>
+      <c r="AK62">
+        <v>-0.02257141394089556</v>
+      </c>
+      <c r="AL62">
+        <v>0.6685256322146611</v>
+      </c>
+      <c r="AM62">
+        <v>0.4059848970405355</v>
+      </c>
+    </row>
+    <row r="63" spans="1:39">
+      <c r="A63" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" t="s">
+        <v>50</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" t="s">
+        <v>51</v>
+      </c>
+      <c r="H63">
+        <v>374</v>
+      </c>
+      <c r="I63" t="s">
+        <v>137</v>
+      </c>
+      <c r="J63" t="s">
+        <v>138</v>
+      </c>
+      <c r="K63" t="s">
+        <v>139</v>
+      </c>
+      <c r="L63" t="s">
+        <v>140</v>
+      </c>
+      <c r="M63">
+        <v>0.5981754751044985</v>
+      </c>
+      <c r="N63">
+        <v>0.1834813107979263</v>
+      </c>
+      <c r="O63">
+        <v>0.238558714104363</v>
+      </c>
+      <c r="P63">
+        <v>0.957792236104634</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>48</v>
+      </c>
+      <c r="R63">
+        <v>1.818797330250516</v>
+      </c>
+      <c r="S63">
+        <v>1.269418236603212</v>
+      </c>
+      <c r="T63">
+        <v>2.605936824555333</v>
+      </c>
+      <c r="U63">
+        <v>3.260143894237206</v>
+      </c>
+      <c r="V63">
+        <v>0.001113557035086027</v>
+      </c>
+      <c r="Z63">
+        <v>876.3712098117336</v>
+      </c>
+      <c r="AA63">
+        <v>0.02442112070292457</v>
+      </c>
+      <c r="AB63">
+        <v>9.275946957166651</v>
+      </c>
+      <c r="AC63">
+        <v>0.7853691226453146</v>
+      </c>
+      <c r="AD63">
+        <v>0.06640540107029785</v>
+      </c>
+      <c r="AE63">
+        <v>0.001556021051854706</v>
+      </c>
+      <c r="AF63">
+        <v>0.1347412409566866</v>
+      </c>
+      <c r="AG63">
+        <v>0.001084774980397903</v>
+      </c>
+      <c r="AH63">
+        <v>5.402772802143296E-05</v>
+      </c>
+      <c r="AI63">
+        <v>-0.03009702198996842</v>
+      </c>
+      <c r="AJ63">
+        <v>0.8796737195551009</v>
+      </c>
+      <c r="AK63">
+        <v>-0.02257141394089556</v>
+      </c>
+      <c r="AL63">
+        <v>0.6685256322146611</v>
+      </c>
+      <c r="AM63">
+        <v>0.4059848970405355</v>
+      </c>
+    </row>
+    <row r="64" spans="1:39">
+      <c r="A64" t="s">
+        <v>143</v>
+      </c>
+      <c r="B64" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64">
+        <v>374</v>
+      </c>
+      <c r="I64" t="s">
+        <v>59</v>
+      </c>
+      <c r="J64" t="s">
+        <v>60</v>
+      </c>
+      <c r="K64" t="s">
+        <v>61</v>
+      </c>
+      <c r="L64" t="s">
+        <v>62</v>
+      </c>
+      <c r="M64">
+        <v>0.5725545597161533</v>
+      </c>
+      <c r="N64">
+        <v>0.08685275537827067</v>
+      </c>
+      <c r="O64">
+        <v>0.4023262872166754</v>
+      </c>
+      <c r="P64">
+        <v>0.7427828322156312</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>48</v>
+      </c>
+      <c r="R64">
+        <v>1.772789969783608</v>
+      </c>
+      <c r="S64">
+        <v>1.495299150085201</v>
+      </c>
+      <c r="T64">
+        <v>2.10177627452426</v>
+      </c>
+      <c r="U64">
+        <v>6.592244048245801</v>
+      </c>
+      <c r="V64">
+        <v>4.332276613561737E-11</v>
+      </c>
+      <c r="W64" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y64">
+        <v>2.372201679219757</v>
+      </c>
+      <c r="Z64">
+        <v>863.68990632628</v>
+      </c>
+      <c r="AA64">
+        <v>0.07226312218892417</v>
+      </c>
+      <c r="AD64">
+        <v>0.05237979493519686</v>
+      </c>
+      <c r="AE64">
+        <v>0.009234004782708955</v>
+      </c>
+      <c r="AF64">
+        <v>0.1450430493851141</v>
+      </c>
+      <c r="AG64">
+        <v>0.0004919759297273739</v>
+      </c>
+      <c r="AH64">
+        <v>0.002780220155882196</v>
+      </c>
+      <c r="AI64">
+        <v>-0.01683452775357725</v>
+      </c>
+      <c r="AJ64">
+        <v>0.7276419199311994</v>
+      </c>
+      <c r="AK64">
+        <v>0.02224862591724975</v>
+      </c>
+      <c r="AL64">
+        <v>0.2870862128902341</v>
+      </c>
+      <c r="AM64">
+        <v>0.6149612582442242</v>
+      </c>
+    </row>
+    <row r="65" spans="1:39">
+      <c r="A65" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" t="b">
+        <v>0</v>
+      </c>
+      <c r="F65" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" t="s">
+        <v>43</v>
+      </c>
+      <c r="H65">
+        <v>374</v>
+      </c>
+      <c r="I65" t="s">
+        <v>137</v>
+      </c>
+      <c r="J65" t="s">
+        <v>138</v>
+      </c>
+      <c r="K65" t="s">
+        <v>139</v>
+      </c>
+      <c r="L65" t="s">
+        <v>140</v>
+      </c>
+      <c r="M65">
+        <v>0.6135694103676462</v>
+      </c>
+      <c r="N65">
+        <v>0.1598819189959375</v>
+      </c>
+      <c r="O65">
+        <v>0.3002066073564585</v>
+      </c>
+      <c r="P65">
+        <v>0.9269322133788339</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>48</v>
+      </c>
+      <c r="R65">
+        <v>1.847012391842623</v>
+      </c>
+      <c r="S65">
+        <v>1.350137727148254</v>
+      </c>
+      <c r="T65">
+        <v>2.526745758616673</v>
+      </c>
+      <c r="U65">
+        <v>3.837641017951735</v>
+      </c>
+      <c r="V65">
+        <v>0.0001242219001388355</v>
+      </c>
+      <c r="Y65">
+        <v>2.372201679219757</v>
+      </c>
+      <c r="Z65">
+        <v>863.68990632628</v>
+      </c>
+      <c r="AA65">
+        <v>0.07226312218892417</v>
+      </c>
+      <c r="AD65">
+        <v>0.05237979493519686</v>
+      </c>
+      <c r="AE65">
+        <v>0.009234004782708955</v>
+      </c>
+      <c r="AF65">
+        <v>0.1450430493851141</v>
+      </c>
+      <c r="AG65">
+        <v>0.0004919759297273739</v>
+      </c>
+      <c r="AH65">
+        <v>0.002780220155882196</v>
+      </c>
+      <c r="AI65">
+        <v>-0.01683452775357725</v>
+      </c>
+      <c r="AJ65">
+        <v>0.7276419199311994</v>
+      </c>
+      <c r="AK65">
+        <v>0.02224862591724975</v>
+      </c>
+      <c r="AL65">
+        <v>0.2870862128902341</v>
+      </c>
+      <c r="AM65">
+        <v>0.6149612582442242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:39">
+      <c r="A66" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" t="s">
+        <v>130</v>
+      </c>
+      <c r="D66" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" t="s">
+        <v>51</v>
+      </c>
+      <c r="H66">
+        <v>374</v>
+      </c>
+      <c r="I66" t="s">
+        <v>59</v>
+      </c>
+      <c r="J66" t="s">
+        <v>60</v>
+      </c>
+      <c r="K66" t="s">
+        <v>61</v>
+      </c>
+      <c r="L66" t="s">
+        <v>62</v>
+      </c>
+      <c r="M66">
+        <v>0.6270847669506074</v>
+      </c>
+      <c r="N66">
+        <v>0.1039411877245562</v>
+      </c>
+      <c r="O66">
+        <v>0.4233637825001607</v>
+      </c>
+      <c r="P66">
+        <v>0.8308057514010543</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>48</v>
+      </c>
+      <c r="R66">
+        <v>1.872144877617715</v>
+      </c>
+      <c r="S66">
+        <v>1.527089723450498</v>
+      </c>
+      <c r="T66">
+        <v>2.295167329703966</v>
+      </c>
+      <c r="U66">
+        <v>6.033072939404736</v>
+      </c>
+      <c r="V66">
+        <v>1.60870758301333E-09</v>
+      </c>
+      <c r="W66" t="s">
+        <v>49</v>
+      </c>
+      <c r="X66" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z66">
+        <v>852.1287123132962</v>
+      </c>
+      <c r="AA66">
+        <v>0.05171942917975758</v>
+      </c>
+      <c r="AB66">
+        <v>8.768717985377998</v>
+      </c>
+      <c r="AC66">
+        <v>0.6904196329129887</v>
+      </c>
+      <c r="AD66">
+        <v>0.05237979493519686</v>
+      </c>
+      <c r="AE66">
+        <v>0.009234004782708955</v>
+      </c>
+      <c r="AF66">
+        <v>0.1450430493851141</v>
+      </c>
+      <c r="AG66">
+        <v>0.0004919759297273739</v>
+      </c>
+      <c r="AH66">
+        <v>0.002780220155882196</v>
+      </c>
+      <c r="AI66">
+        <v>-0.01683452775357725</v>
+      </c>
+      <c r="AJ66">
+        <v>0.7276419199311994</v>
+      </c>
+      <c r="AK66">
+        <v>0.02224862591724975</v>
+      </c>
+      <c r="AL66">
+        <v>0.2870862128902341</v>
+      </c>
+      <c r="AM66">
+        <v>0.6149612582442242</v>
+      </c>
+    </row>
+    <row r="67" spans="1:39">
+      <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" t="s">
+        <v>50</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" t="s">
+        <v>51</v>
+      </c>
+      <c r="H67">
+        <v>374</v>
+      </c>
+      <c r="I67" t="s">
+        <v>137</v>
+      </c>
+      <c r="J67" t="s">
+        <v>138</v>
+      </c>
+      <c r="K67" t="s">
+        <v>139</v>
+      </c>
+      <c r="L67" t="s">
+        <v>140</v>
+      </c>
+      <c r="M67">
+        <v>0.5192925041783603</v>
+      </c>
+      <c r="N67">
+        <v>0.1751443833098721</v>
+      </c>
+      <c r="O67">
+        <v>0.1760158207965329</v>
+      </c>
+      <c r="P67">
+        <v>0.8625691875601876</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>48</v>
+      </c>
+      <c r="R67">
+        <v>1.680838043035335</v>
+      </c>
+      <c r="S67">
+        <v>1.192456924119806</v>
+      </c>
+      <c r="T67">
+        <v>2.369239902732961</v>
+      </c>
+      <c r="U67">
+        <v>2.964939522266085</v>
+      </c>
+      <c r="V67">
+        <v>0.003027424387804036</v>
+      </c>
+      <c r="Z67">
+        <v>852.1287123132962</v>
+      </c>
+      <c r="AA67">
+        <v>0.05171942917975758</v>
+      </c>
+      <c r="AB67">
+        <v>8.768717985377998</v>
+      </c>
+      <c r="AC67">
+        <v>0.6904196329129887</v>
+      </c>
+      <c r="AD67">
+        <v>0.05237979493519686</v>
+      </c>
+      <c r="AE67">
+        <v>0.009234004782708955</v>
+      </c>
+      <c r="AF67">
+        <v>0.1450430493851141</v>
+      </c>
+      <c r="AG67">
+        <v>0.0004919759297273739</v>
+      </c>
+      <c r="AH67">
+        <v>0.002780220155882196</v>
+      </c>
+      <c r="AI67">
+        <v>-0.01683452775357725</v>
+      </c>
+      <c r="AJ67">
+        <v>0.7276419199311994</v>
+      </c>
+      <c r="AK67">
+        <v>0.02224862591724975</v>
+      </c>
+      <c r="AL67">
+        <v>0.2870862128902341</v>
+      </c>
+      <c r="AM67">
+        <v>0.6149612582442242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:39">
+      <c r="A68" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" t="s">
+        <v>130</v>
+      </c>
+      <c r="D68" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" t="s">
+        <v>43</v>
+      </c>
+      <c r="H68">
+        <v>374</v>
+      </c>
+      <c r="I68" t="s">
+        <v>64</v>
+      </c>
+      <c r="J68" t="s">
+        <v>65</v>
+      </c>
+      <c r="K68" t="s">
+        <v>66</v>
+      </c>
+      <c r="L68" t="s">
+        <v>67</v>
+      </c>
+      <c r="M68">
+        <v>-0.260152895039903</v>
+      </c>
+      <c r="N68">
+        <v>0.07069882298733642</v>
+      </c>
+      <c r="O68">
+        <v>-0.3987200418444549</v>
+      </c>
+      <c r="P68">
+        <v>-0.1215857482353512</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>48</v>
+      </c>
+      <c r="R68">
+        <v>0.7709337048525235</v>
+      </c>
+      <c r="S68">
+        <v>0.6711785769700132</v>
+      </c>
+      <c r="T68">
+        <v>0.885515118734476</v>
+      </c>
+      <c r="U68">
+        <v>-3.679734457340282</v>
+      </c>
+      <c r="V68">
+        <v>0.0002334769455181231</v>
+      </c>
+      <c r="W68" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y68">
+        <v>1.608515033144837</v>
+      </c>
+      <c r="Z68">
+        <v>889.6223938023383</v>
+      </c>
+      <c r="AA68">
+        <v>0.0441471834743925</v>
+      </c>
+      <c r="AD68">
+        <v>0.04157241014854481</v>
+      </c>
+      <c r="AE68">
+        <v>0.02911281038124679</v>
+      </c>
+      <c r="AF68">
+        <v>0.1413933523923987</v>
+      </c>
+      <c r="AG68">
+        <v>0.000653334558262665</v>
+      </c>
+      <c r="AH68">
+        <v>0.000412464935322765</v>
+      </c>
+      <c r="AI68">
+        <v>-0.02780125008513723</v>
+      </c>
+      <c r="AJ68">
+        <v>0.8588465959124301</v>
+      </c>
+      <c r="AK68">
+        <v>0.01103194008204742</v>
+      </c>
+      <c r="AL68">
+        <v>0.3774171286614489</v>
+      </c>
+      <c r="AM68">
+        <v>0.6062188911113042</v>
+      </c>
+    </row>
+    <row r="69" spans="1:39">
+      <c r="A69" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" t="s">
+        <v>43</v>
+      </c>
+      <c r="H69">
+        <v>374</v>
+      </c>
+      <c r="I69" t="s">
+        <v>137</v>
+      </c>
+      <c r="J69" t="s">
+        <v>138</v>
+      </c>
+      <c r="K69" t="s">
+        <v>139</v>
+      </c>
+      <c r="L69" t="s">
+        <v>140</v>
+      </c>
+      <c r="M69">
+        <v>0.7163065542999526</v>
+      </c>
+      <c r="N69">
+        <v>0.1653906441822401</v>
+      </c>
+      <c r="O69">
+        <v>0.392146848322883</v>
+      </c>
+      <c r="P69">
+        <v>1.040466260277022</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>48</v>
+      </c>
+      <c r="R69">
+        <v>2.046859268717638</v>
+      </c>
+      <c r="S69">
+        <v>1.480155053730967</v>
+      </c>
+      <c r="T69">
+        <v>2.830536473442204</v>
+      </c>
+      <c r="U69">
+        <v>4.330998031005133</v>
+      </c>
+      <c r="V69">
+        <v>1.484350093777515E-05</v>
+      </c>
+      <c r="Y69">
+        <v>1.608515033144837</v>
+      </c>
+      <c r="Z69">
+        <v>889.6223938023383</v>
+      </c>
+      <c r="AA69">
+        <v>0.0441471834743925</v>
+      </c>
+      <c r="AD69">
+        <v>0.04157241014854481</v>
+      </c>
+      <c r="AE69">
+        <v>0.02911281038124679</v>
+      </c>
+      <c r="AF69">
+        <v>0.1413933523923987</v>
+      </c>
+      <c r="AG69">
+        <v>0.000653334558262665</v>
+      </c>
+      <c r="AH69">
+        <v>0.000412464935322765</v>
+      </c>
+      <c r="AI69">
+        <v>-0.02780125008513723</v>
+      </c>
+      <c r="AJ69">
+        <v>0.8588465959124301</v>
+      </c>
+      <c r="AK69">
+        <v>0.01103194008204742</v>
+      </c>
+      <c r="AL69">
+        <v>0.3774171286614489</v>
+      </c>
+      <c r="AM69">
+        <v>0.6062188911113042</v>
+      </c>
+    </row>
+    <row r="70" spans="1:39">
+      <c r="A70" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" t="s">
+        <v>130</v>
+      </c>
+      <c r="D70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" t="s">
+        <v>51</v>
+      </c>
+      <c r="H70">
+        <v>374</v>
+      </c>
+      <c r="I70" t="s">
+        <v>64</v>
+      </c>
+      <c r="J70" t="s">
+        <v>65</v>
+      </c>
+      <c r="K70" t="s">
+        <v>66</v>
+      </c>
+      <c r="L70" t="s">
+        <v>67</v>
+      </c>
+      <c r="M70">
+        <v>-0.2717681813362952</v>
+      </c>
+      <c r="N70">
+        <v>0.07887080517893175</v>
+      </c>
+      <c r="O70">
+        <v>-0.4263521189186766</v>
+      </c>
+      <c r="P70">
+        <v>-0.1171842437539138</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>48</v>
+      </c>
+      <c r="R70">
+        <v>0.7620308935991463</v>
+      </c>
+      <c r="S70">
+        <v>0.6528864079849734</v>
+      </c>
+      <c r="T70">
+        <v>0.8894213077458926</v>
+      </c>
+      <c r="U70">
+        <v>-3.445738644606749</v>
+      </c>
+      <c r="V70">
+        <v>0.0005695008650493622</v>
+      </c>
+      <c r="W70" t="s">
+        <v>68</v>
+      </c>
+      <c r="X70" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z70">
+        <v>873.6467951024277</v>
+      </c>
+      <c r="AA70">
+        <v>0.02748895285009689</v>
+      </c>
+      <c r="AB70">
+        <v>6.895799027962267</v>
+      </c>
+      <c r="AC70">
+        <v>0.7732506852344031</v>
+      </c>
+      <c r="AD70">
+        <v>0.04157241014854481</v>
+      </c>
+      <c r="AE70">
+        <v>0.02911281038124679</v>
+      </c>
+      <c r="AF70">
+        <v>0.1413933523923987</v>
+      </c>
+      <c r="AG70">
+        <v>0.000653334558262665</v>
+      </c>
+      <c r="AH70">
+        <v>0.000412464935322765</v>
+      </c>
+      <c r="AI70">
+        <v>-0.02780125008513723</v>
+      </c>
+      <c r="AJ70">
+        <v>0.8588465959124301</v>
+      </c>
+      <c r="AK70">
+        <v>0.01103194008204742</v>
+      </c>
+      <c r="AL70">
+        <v>0.3774171286614489</v>
+      </c>
+      <c r="AM70">
+        <v>0.6062188911113042</v>
+      </c>
+    </row>
+    <row r="71" spans="1:39">
+      <c r="A71" t="s">
+        <v>144</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" t="s">
+        <v>130</v>
+      </c>
+      <c r="D71" t="s">
+        <v>50</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" t="s">
+        <v>51</v>
+      </c>
+      <c r="H71">
+        <v>374</v>
+      </c>
+      <c r="I71" t="s">
+        <v>137</v>
+      </c>
+      <c r="J71" t="s">
+        <v>138</v>
+      </c>
+      <c r="K71" t="s">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s">
+        <v>140</v>
+      </c>
+      <c r="M71">
+        <v>0.5668646676806111</v>
+      </c>
+      <c r="N71">
+        <v>0.1825870407126509</v>
+      </c>
+      <c r="O71">
+        <v>0.2090006438400669</v>
+      </c>
+      <c r="P71">
+        <v>0.9247286915211552</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>48</v>
+      </c>
+      <c r="R71">
+        <v>1.762731628827339</v>
+      </c>
+      <c r="S71">
+        <v>1.232445792027981</v>
+      </c>
+      <c r="T71">
+        <v>2.521184148923396</v>
+      </c>
+      <c r="U71">
+        <v>3.104627061526907</v>
+      </c>
+      <c r="V71">
+        <v>0.001905190773640427</v>
+      </c>
+      <c r="Z71">
+        <v>873.6467951024277</v>
+      </c>
+      <c r="AA71">
+        <v>0.02748895285009689</v>
+      </c>
+      <c r="AB71">
+        <v>6.895799027962267</v>
+      </c>
+      <c r="AC71">
+        <v>0.7732506852344031</v>
+      </c>
+      <c r="AD71">
+        <v>0.04157241014854481</v>
+      </c>
+      <c r="AE71">
+        <v>0.02911281038124679</v>
+      </c>
+      <c r="AF71">
+        <v>0.1413933523923987</v>
+      </c>
+      <c r="AG71">
+        <v>0.000653334558262665</v>
+      </c>
+      <c r="AH71">
+        <v>0.000412464935322765</v>
+      </c>
+      <c r="AI71">
+        <v>-0.02780125008513723</v>
+      </c>
+      <c r="AJ71">
+        <v>0.8588465959124301</v>
+      </c>
+      <c r="AK71">
+        <v>0.01103194008204742</v>
+      </c>
+      <c r="AL71">
+        <v>0.3774171286614489</v>
+      </c>
+      <c r="AM71">
+        <v>0.6062188911113042</v>
+      </c>
+    </row>
+    <row r="72" spans="1:39">
+      <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" t="s">
+        <v>41</v>
+      </c>
+      <c r="E72" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" t="s">
+        <v>43</v>
+      </c>
+      <c r="H72">
+        <v>374</v>
+      </c>
+      <c r="I72" t="s">
+        <v>70</v>
+      </c>
+      <c r="J72" t="s">
+        <v>71</v>
+      </c>
+      <c r="K72" t="s">
+        <v>72</v>
+      </c>
+      <c r="L72" t="s">
+        <v>67</v>
+      </c>
+      <c r="M72">
+        <v>-1.565219491370258</v>
+      </c>
+      <c r="N72">
+        <v>0.5149275551604164</v>
+      </c>
+      <c r="O72">
+        <v>-2.574458954131936</v>
+      </c>
+      <c r="P72">
+        <v>-0.5559800286085794</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>48</v>
+      </c>
+      <c r="R72">
+        <v>0.209042125194959</v>
+      </c>
+      <c r="S72">
+        <v>0.07619503665806163</v>
+      </c>
+      <c r="T72">
+        <v>0.5735099295526288</v>
+      </c>
+      <c r="U72">
+        <v>-3.039688740064884</v>
+      </c>
+      <c r="V72">
+        <v>0.002368227623466692</v>
+      </c>
+      <c r="W72" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y72">
+        <v>1.574180506107326</v>
+      </c>
+      <c r="Z72">
+        <v>893.6597567149735</v>
+      </c>
+      <c r="AA72">
+        <v>0.03976988460073927</v>
+      </c>
+      <c r="AD72">
+        <v>0.05053246693891127</v>
+      </c>
+      <c r="AE72">
+        <v>0.01137952668416091</v>
+      </c>
+      <c r="AF72">
+        <v>0.1413882072688612</v>
+      </c>
+      <c r="AG72">
+        <v>0.0006536693718390929</v>
+      </c>
+      <c r="AH72">
+        <v>0.000288062679427048</v>
+      </c>
+      <c r="AI72">
+        <v>-0.02313018798661179</v>
+      </c>
+      <c r="AJ72">
+        <v>0.8092698679079393</v>
+      </c>
+      <c r="AK72">
+        <v>0.01281201723542385</v>
+      </c>
+      <c r="AL72">
+        <v>0.3624590882212144</v>
+      </c>
+      <c r="AM72">
+        <v>0.7467533296566606</v>
+      </c>
+    </row>
+    <row r="73" spans="1:39">
+      <c r="A73" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" t="s">
+        <v>130</v>
+      </c>
+      <c r="D73" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" t="s">
+        <v>43</v>
+      </c>
+      <c r="H73">
+        <v>374</v>
+      </c>
+      <c r="I73" t="s">
+        <v>137</v>
+      </c>
+      <c r="J73" t="s">
+        <v>138</v>
+      </c>
+      <c r="K73" t="s">
+        <v>139</v>
+      </c>
+      <c r="L73" t="s">
+        <v>140</v>
+      </c>
+      <c r="M73">
+        <v>0.7463287307681975</v>
+      </c>
+      <c r="N73">
+        <v>0.1649692361005428</v>
+      </c>
+      <c r="O73">
+        <v>0.4229949694540488</v>
+      </c>
+      <c r="P73">
+        <v>1.069662492082346</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>48</v>
+      </c>
+      <c r="R73">
+        <v>2.109242188838638</v>
+      </c>
+      <c r="S73">
+        <v>1.52652661668485</v>
+      </c>
+      <c r="T73">
+        <v>2.914395702341873</v>
+      </c>
+      <c r="U73">
+        <v>4.524047928022999</v>
+      </c>
+      <c r="V73">
+        <v>6.066797660895452E-06</v>
+      </c>
+      <c r="Y73">
+        <v>1.574180506107326</v>
+      </c>
+      <c r="Z73">
+        <v>893.6597567149735</v>
+      </c>
+      <c r="AA73">
+        <v>0.03976988460073927</v>
+      </c>
+      <c r="AD73">
+        <v>0.05053246693891127</v>
+      </c>
+      <c r="AE73">
+        <v>0.01137952668416091</v>
+      </c>
+      <c r="AF73">
+        <v>0.1413882072688612</v>
+      </c>
+      <c r="AG73">
+        <v>0.0006536693718390929</v>
+      </c>
+      <c r="AH73">
+        <v>0.000288062679427048</v>
+      </c>
+      <c r="AI73">
+        <v>-0.02313018798661179</v>
+      </c>
+      <c r="AJ73">
+        <v>0.8092698679079393</v>
+      </c>
+      <c r="AK73">
+        <v>0.01281201723542385</v>
+      </c>
+      <c r="AL73">
+        <v>0.3624590882212144</v>
+      </c>
+      <c r="AM73">
+        <v>0.7467533296566606</v>
+      </c>
+    </row>
+    <row r="74" spans="1:39">
+      <c r="A74" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C74" t="s">
+        <v>130</v>
+      </c>
+      <c r="D74" t="s">
+        <v>50</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" t="s">
+        <v>51</v>
+      </c>
+      <c r="H74">
+        <v>374</v>
+      </c>
+      <c r="I74" t="s">
+        <v>70</v>
+      </c>
+      <c r="J74" t="s">
+        <v>71</v>
+      </c>
+      <c r="K74" t="s">
+        <v>72</v>
+      </c>
+      <c r="L74" t="s">
+        <v>67</v>
+      </c>
+      <c r="M74">
+        <v>-1.396839436581202</v>
+      </c>
+      <c r="N74">
+        <v>0.5400773243137135</v>
+      </c>
+      <c r="O74">
+        <v>-2.455371541102839</v>
+      </c>
+      <c r="P74">
+        <v>-0.3383073320595649</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>48</v>
+      </c>
+      <c r="R74">
+        <v>0.2473775822320234</v>
+      </c>
+      <c r="S74">
+        <v>0.08583129966050305</v>
+      </c>
+      <c r="T74">
+        <v>0.7129761337998457</v>
+      </c>
+      <c r="U74">
+        <v>-2.586369346937852</v>
+      </c>
+      <c r="V74">
+        <v>0.009699293432254846</v>
+      </c>
+      <c r="W74" t="s">
+        <v>68</v>
+      </c>
+      <c r="X74" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z74">
+        <v>878.7008424128406</v>
+      </c>
+      <c r="AA74">
+        <v>0.02179783366796428</v>
+      </c>
+      <c r="AB74">
+        <v>6.99459565219997</v>
+      </c>
+      <c r="AC74">
+        <v>0.780966866528612</v>
+      </c>
+      <c r="AD74">
+        <v>0.05053246693891127</v>
+      </c>
+      <c r="AE74">
+        <v>0.01137952668416091</v>
+      </c>
+      <c r="AF74">
+        <v>0.1413882072688612</v>
+      </c>
+      <c r="AG74">
+        <v>0.0006536693718390929</v>
+      </c>
+      <c r="AH74">
+        <v>0.000288062679427048</v>
+      </c>
+      <c r="AI74">
+        <v>-0.02313018798661179</v>
+      </c>
+      <c r="AJ74">
+        <v>0.8092698679079393</v>
+      </c>
+      <c r="AK74">
+        <v>0.01281201723542385</v>
+      </c>
+      <c r="AL74">
+        <v>0.3624590882212144</v>
+      </c>
+      <c r="AM74">
+        <v>0.7467533296566606</v>
+      </c>
+    </row>
+    <row r="75" spans="1:39">
+      <c r="A75" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" t="s">
+        <v>51</v>
+      </c>
+      <c r="H75">
+        <v>374</v>
+      </c>
+      <c r="I75" t="s">
+        <v>137</v>
+      </c>
+      <c r="J75" t="s">
+        <v>138</v>
+      </c>
+      <c r="K75" t="s">
+        <v>139</v>
+      </c>
+      <c r="L75" t="s">
+        <v>140</v>
+      </c>
+      <c r="M75">
+        <v>0.597716952263685</v>
+      </c>
+      <c r="N75">
+        <v>0.1837472226899765</v>
+      </c>
+      <c r="O75">
+        <v>0.2375790135320701</v>
+      </c>
+      <c r="P75">
+        <v>0.9578548909953</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>48</v>
+      </c>
+      <c r="R75">
+        <v>1.817963561297448</v>
+      </c>
+      <c r="S75">
+        <v>1.268175195833634</v>
+      </c>
+      <c r="T75">
+        <v>2.606100104357244</v>
+      </c>
+      <c r="U75">
+        <v>3.252930539647774</v>
+      </c>
+      <c r="V75">
+        <v>0.001142214143928568</v>
+      </c>
+      <c r="Z75">
+        <v>878.7008424128406</v>
+      </c>
+      <c r="AA75">
+        <v>0.02179783366796428</v>
+      </c>
+      <c r="AB75">
+        <v>6.99459565219997</v>
+      </c>
+      <c r="AC75">
+        <v>0.780966866528612</v>
+      </c>
+      <c r="AD75">
+        <v>0.05053246693891127</v>
+      </c>
+      <c r="AE75">
+        <v>0.01137952668416091</v>
+      </c>
+      <c r="AF75">
+        <v>0.1413882072688612</v>
+      </c>
+      <c r="AG75">
+        <v>0.0006536693718390929</v>
+      </c>
+      <c r="AH75">
+        <v>0.000288062679427048</v>
+      </c>
+      <c r="AI75">
+        <v>-0.02313018798661179</v>
+      </c>
+      <c r="AJ75">
+        <v>0.8092698679079393</v>
+      </c>
+      <c r="AK75">
+        <v>0.01281201723542385</v>
+      </c>
+      <c r="AL75">
+        <v>0.3624590882212144</v>
+      </c>
+      <c r="AM75">
+        <v>0.7467533296566606</v>
+      </c>
+    </row>
+    <row r="76" spans="1:39">
+      <c r="A76" t="s">
+        <v>146</v>
+      </c>
+      <c r="B76" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" t="s">
+        <v>130</v>
+      </c>
+      <c r="D76" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" t="s">
+        <v>43</v>
+      </c>
+      <c r="H76">
+        <v>374</v>
+      </c>
+      <c r="I76" t="s">
+        <v>74</v>
+      </c>
+      <c r="J76" t="s">
+        <v>75</v>
+      </c>
+      <c r="K76" t="s">
+        <v>76</v>
+      </c>
+      <c r="L76" t="s">
+        <v>67</v>
+      </c>
+      <c r="M76">
+        <v>-0.2634273827188029</v>
+      </c>
+      <c r="N76">
+        <v>0.07606347582698254</v>
+      </c>
+      <c r="O76">
+        <v>-0.4125090558786216</v>
+      </c>
+      <c r="P76">
+        <v>-0.1143457095589841</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>48</v>
+      </c>
+      <c r="R76">
+        <v>0.7684134205066845</v>
+      </c>
+      <c r="S76">
+        <v>0.661987201787941</v>
+      </c>
+      <c r="T76">
+        <v>0.8919495470909854</v>
+      </c>
+      <c r="U76">
+        <v>-3.463257231604914</v>
+      </c>
+      <c r="V76">
+        <v>0.0005336779360685381</v>
+      </c>
+      <c r="W76" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y76">
+        <v>1.586743624662346</v>
+      </c>
+      <c r="Z76">
+        <v>891.4353022188762</v>
+      </c>
+      <c r="AA76">
+        <v>0.04218163265781538</v>
+      </c>
+      <c r="AD76">
+        <v>0.04626208851678131</v>
+      </c>
+      <c r="AE76">
+        <v>0.0180974161502353</v>
+      </c>
+      <c r="AF76">
+        <v>0.1452739850500292</v>
+      </c>
+      <c r="AG76">
+        <v>0.0004817949968795669</v>
+      </c>
+      <c r="AH76">
+        <v>0.000222285194164451</v>
+      </c>
+      <c r="AI76">
+        <v>-0.02792104761414305</v>
+      </c>
+      <c r="AJ76">
+        <v>0.8599920808846813</v>
+      </c>
+      <c r="AK76">
+        <v>0.006237608901293972</v>
+      </c>
+      <c r="AL76">
+        <v>0.418578155164441</v>
+      </c>
+      <c r="AM76">
+        <v>0.5601836188179743</v>
+      </c>
+    </row>
+    <row r="77" spans="1:39">
+      <c r="A77" t="s">
+        <v>146</v>
+      </c>
+      <c r="B77" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" t="s">
+        <v>130</v>
+      </c>
+      <c r="D77" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" t="b">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>42</v>
+      </c>
+      <c r="G77" t="s">
+        <v>43</v>
+      </c>
+      <c r="H77">
+        <v>374</v>
+      </c>
+      <c r="I77" t="s">
+        <v>137</v>
+      </c>
+      <c r="J77" t="s">
+        <v>138</v>
+      </c>
+      <c r="K77" t="s">
+        <v>139</v>
+      </c>
+      <c r="L77" t="s">
+        <v>140</v>
+      </c>
+      <c r="M77">
+        <v>0.7260258157451458</v>
+      </c>
+      <c r="N77">
+        <v>0.1654355769149404</v>
+      </c>
+      <c r="O77">
+        <v>0.4017780432302567</v>
+      </c>
+      <c r="P77">
+        <v>1.050273588260035</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>48</v>
+      </c>
+      <c r="R77">
+        <v>2.066850220366031</v>
+      </c>
+      <c r="S77">
+        <v>1.494479585999339</v>
+      </c>
+      <c r="T77">
+        <v>2.858433044818455</v>
+      </c>
+      <c r="U77">
+        <v>4.388571244977348</v>
+      </c>
+      <c r="V77">
+        <v>1.140977579382347E-05</v>
+      </c>
+      <c r="Y77">
+        <v>1.586743624662346</v>
+      </c>
+      <c r="Z77">
+        <v>891.4353022188762</v>
+      </c>
+      <c r="AA77">
+        <v>0.04218163265781538</v>
+      </c>
+      <c r="AD77">
+        <v>0.04626208851678131</v>
+      </c>
+      <c r="AE77">
+        <v>0.0180974161502353</v>
+      </c>
+      <c r="AF77">
+        <v>0.1452739850500292</v>
+      </c>
+      <c r="AG77">
+        <v>0.0004817949968795669</v>
+      </c>
+      <c r="AH77">
+        <v>0.000222285194164451</v>
+      </c>
+      <c r="AI77">
+        <v>-0.02792104761414305</v>
+      </c>
+      <c r="AJ77">
+        <v>0.8599920808846813</v>
+      </c>
+      <c r="AK77">
+        <v>0.006237608901293972</v>
+      </c>
+      <c r="AL77">
+        <v>0.418578155164441</v>
+      </c>
+      <c r="AM77">
+        <v>0.5601836188179743</v>
+      </c>
+    </row>
+    <row r="78" spans="1:39">
+      <c r="A78" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" t="s">
+        <v>130</v>
+      </c>
+      <c r="D78" t="s">
+        <v>50</v>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" t="s">
+        <v>51</v>
+      </c>
+      <c r="H78">
+        <v>374</v>
+      </c>
+      <c r="I78" t="s">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s">
+        <v>75</v>
+      </c>
+      <c r="K78" t="s">
+        <v>76</v>
+      </c>
+      <c r="L78" t="s">
+        <v>67</v>
+      </c>
+      <c r="M78">
+        <v>-0.2776864626240098</v>
+      </c>
+      <c r="N78">
+        <v>0.08531505579062452</v>
+      </c>
+      <c r="O78">
+        <v>-0.4449008993126592</v>
+      </c>
+      <c r="P78">
+        <v>-0.1104720259353603</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>48</v>
+      </c>
+      <c r="R78">
+        <v>0.7575342995997814</v>
+      </c>
+      <c r="S78">
+        <v>0.6408877853053926</v>
+      </c>
+      <c r="T78">
+        <v>0.895411378134909</v>
+      </c>
+      <c r="U78">
+        <v>-3.254835386915675</v>
+      </c>
+      <c r="V78">
+        <v>0.001134581074584639</v>
+      </c>
+      <c r="W78" t="s">
+        <v>68</v>
+      </c>
+      <c r="X78" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z78">
+        <v>875.098759899526</v>
+      </c>
+      <c r="AA78">
+        <v>0.02585396524491124</v>
+      </c>
+      <c r="AB78">
+        <v>7.021069473420229</v>
+      </c>
+      <c r="AC78">
+        <v>0.7779011509136127</v>
+      </c>
+      <c r="AD78">
+        <v>0.04626208851678131</v>
+      </c>
+      <c r="AE78">
+        <v>0.0180974161502353</v>
+      </c>
+      <c r="AF78">
+        <v>0.1452739850500292</v>
+      </c>
+      <c r="AG78">
+        <v>0.0004817949968795669</v>
+      </c>
+      <c r="AH78">
+        <v>0.000222285194164451</v>
+      </c>
+      <c r="AI78">
+        <v>-0.02792104761414305</v>
+      </c>
+      <c r="AJ78">
+        <v>0.8599920808846813</v>
+      </c>
+      <c r="AK78">
+        <v>0.006237608901293972</v>
+      </c>
+      <c r="AL78">
+        <v>0.418578155164441</v>
+      </c>
+      <c r="AM78">
+        <v>0.5601836188179743</v>
+      </c>
+    </row>
+    <row r="79" spans="1:39">
+      <c r="A79" t="s">
+        <v>146</v>
+      </c>
+      <c r="B79" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79" t="s">
+        <v>130</v>
+      </c>
+      <c r="D79" t="s">
+        <v>50</v>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>51</v>
+      </c>
+      <c r="H79">
+        <v>374</v>
+      </c>
+      <c r="I79" t="s">
+        <v>137</v>
+      </c>
+      <c r="J79" t="s">
+        <v>138</v>
+      </c>
+      <c r="K79" t="s">
+        <v>139</v>
+      </c>
+      <c r="L79" t="s">
+        <v>140</v>
+      </c>
+      <c r="M79">
+        <v>0.5731871896438278</v>
+      </c>
+      <c r="N79">
+        <v>0.1828612928898245</v>
+      </c>
+      <c r="O79">
+        <v>0.2147856414133415</v>
+      </c>
+      <c r="P79">
+        <v>0.931588737874314</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>48</v>
+      </c>
+      <c r="R79">
+        <v>1.773911844602351</v>
+      </c>
+      <c r="S79">
+        <v>1.239596150405723</v>
+      </c>
+      <c r="T79">
+        <v>2.538539048697893</v>
+      </c>
+      <c r="U79">
+        <v>3.134546303296553</v>
+      </c>
+      <c r="V79">
+        <v>0.001721200876586472</v>
+      </c>
+      <c r="Z79">
+        <v>875.098759899526</v>
+      </c>
+      <c r="AA79">
+        <v>0.02585396524491124</v>
+      </c>
+      <c r="AB79">
+        <v>7.021069473420229</v>
+      </c>
+      <c r="AC79">
+        <v>0.7779011509136127</v>
+      </c>
+      <c r="AD79">
+        <v>0.04626208851678131</v>
+      </c>
+      <c r="AE79">
+        <v>0.0180974161502353</v>
+      </c>
+      <c r="AF79">
+        <v>0.1452739850500292</v>
+      </c>
+      <c r="AG79">
+        <v>0.0004817949968795669</v>
+      </c>
+      <c r="AH79">
+        <v>0.000222285194164451</v>
+      </c>
+      <c r="AI79">
+        <v>-0.02792104761414305</v>
+      </c>
+      <c r="AJ79">
+        <v>0.8599920808846813</v>
+      </c>
+      <c r="AK79">
+        <v>0.006237608901293972</v>
+      </c>
+      <c r="AL79">
+        <v>0.418578155164441</v>
+      </c>
+      <c r="AM79">
+        <v>0.5601836188179743</v>
+      </c>
+    </row>
+    <row r="80" spans="1:39">
+      <c r="A80" t="s">
+        <v>147</v>
+      </c>
+      <c r="B80" t="s">
+        <v>110</v>
+      </c>
+      <c r="C80" t="s">
+        <v>130</v>
+      </c>
+      <c r="D80" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" t="s">
+        <v>43</v>
+      </c>
+      <c r="H80">
+        <v>374</v>
+      </c>
+      <c r="I80" t="s">
+        <v>113</v>
+      </c>
+      <c r="J80" t="s">
+        <v>114</v>
+      </c>
+      <c r="K80" t="s">
+        <v>115</v>
+      </c>
+      <c r="L80" t="s">
+        <v>116</v>
+      </c>
+      <c r="M80">
+        <v>0.4332056140575093</v>
+      </c>
+      <c r="N80">
+        <v>0.1173776195123302</v>
+      </c>
+      <c r="O80">
+        <v>0.2031497072222963</v>
+      </c>
+      <c r="P80">
+        <v>0.6632615208927224</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>48</v>
+      </c>
+      <c r="R80">
+        <v>1.542193284721841</v>
+      </c>
+      <c r="S80">
+        <v>1.225255884172834</v>
+      </c>
+      <c r="T80">
+        <v>1.941113001915321</v>
+      </c>
+      <c r="U80">
+        <v>3.690700287306494</v>
+      </c>
+      <c r="V80">
+        <v>0.0002236375183896802</v>
+      </c>
+      <c r="W80" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y80">
+        <v>1.929083492303374</v>
+      </c>
+      <c r="Z80">
+        <v>880.8076632166324</v>
+      </c>
+      <c r="AA80">
+        <v>0.0558724875989044</v>
+      </c>
+      <c r="AD80">
+        <v>0.02898360482091776</v>
+      </c>
+      <c r="AE80">
+        <v>0.08768723883412551</v>
+      </c>
+      <c r="AF80">
+        <v>0.1155953897232893</v>
+      </c>
+      <c r="AG80">
+        <v>0.004145194438372662</v>
+      </c>
+      <c r="AH80">
+        <v>0.122045497978154</v>
+      </c>
+      <c r="AI80">
+        <v>-0.0119301575738107</v>
+      </c>
+      <c r="AJ80">
+        <v>0.6538934426249396</v>
+      </c>
+      <c r="AK80">
+        <v>0.03892970025733097</v>
+      </c>
+      <c r="AL80">
+        <v>0.1753202809164403</v>
+      </c>
+      <c r="AM80">
+        <v>0.8228564066085329</v>
+      </c>
+    </row>
+    <row r="81" spans="1:39">
+      <c r="A81" t="s">
+        <v>147</v>
+      </c>
+      <c r="B81" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" t="s">
+        <v>130</v>
+      </c>
+      <c r="D81" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" t="s">
+        <v>43</v>
+      </c>
+      <c r="H81">
+        <v>374</v>
+      </c>
+      <c r="I81" t="s">
+        <v>121</v>
+      </c>
+      <c r="J81" t="s">
+        <v>122</v>
+      </c>
+      <c r="K81" t="s">
+        <v>123</v>
+      </c>
+      <c r="L81" t="s">
+        <v>124</v>
+      </c>
+      <c r="M81">
+        <v>-0.1550178038009967</v>
+      </c>
+      <c r="N81">
+        <v>0.04143937532527005</v>
+      </c>
+      <c r="O81">
+        <v>-0.2362374869803638</v>
+      </c>
+      <c r="P81">
+        <v>-0.07379812062162962</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>48</v>
+      </c>
+      <c r="R81">
+        <v>0.8563999301739535</v>
+      </c>
+      <c r="S81">
+        <v>0.7895931335754788</v>
+      </c>
+      <c r="T81">
+        <v>0.9288591924309626</v>
+      </c>
+      <c r="U81">
+        <v>-3.740833508811742</v>
+      </c>
+      <c r="V81">
+        <v>0.000183410992071168</v>
+      </c>
+      <c r="W81" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y81">
+        <v>1.929083492303374</v>
+      </c>
+      <c r="Z81">
+        <v>880.8076632166324</v>
+      </c>
+      <c r="AA81">
+        <v>0.0558724875989044</v>
+      </c>
+      <c r="AD81">
+        <v>0.02898360482091776</v>
+      </c>
+      <c r="AE81">
+        <v>0.08768723883412551</v>
+      </c>
+      <c r="AF81">
+        <v>0.1155953897232893</v>
+      </c>
+      <c r="AG81">
+        <v>0.004145194438372662</v>
+      </c>
+      <c r="AH81">
+        <v>0.122045497978154</v>
+      </c>
+      <c r="AI81">
+        <v>-0.0119301575738107</v>
+      </c>
+      <c r="AJ81">
+        <v>0.6538934426249396</v>
+      </c>
+      <c r="AK81">
+        <v>0.03892970025733097</v>
+      </c>
+      <c r="AL81">
+        <v>0.1753202809164403</v>
+      </c>
+      <c r="AM81">
+        <v>0.8228564066085329</v>
+      </c>
+    </row>
+    <row r="82" spans="1:39">
+      <c r="A82" t="s">
+        <v>147</v>
+      </c>
+      <c r="B82" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" t="s">
+        <v>130</v>
+      </c>
+      <c r="D82" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" t="b">
+        <v>0</v>
+      </c>
+      <c r="F82" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" t="s">
+        <v>43</v>
+      </c>
+      <c r="H82">
+        <v>374</v>
+      </c>
+      <c r="I82" t="s">
+        <v>137</v>
+      </c>
+      <c r="J82" t="s">
+        <v>138</v>
+      </c>
+      <c r="K82" t="s">
+        <v>139</v>
+      </c>
+      <c r="L82" t="s">
+        <v>140</v>
+      </c>
+      <c r="M82">
+        <v>0.6514891258447828</v>
+      </c>
+      <c r="N82">
+        <v>0.1654739628380105</v>
+      </c>
+      <c r="O82">
+        <v>0.327166118303163</v>
+      </c>
+      <c r="P82">
+        <v>0.9758121333864026</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>48</v>
+      </c>
+      <c r="R82">
+        <v>1.918395435275591</v>
+      </c>
+      <c r="S82">
+        <v>1.38703186942417</v>
+      </c>
+      <c r="T82">
+        <v>2.653321186927081</v>
+      </c>
+      <c r="U82">
+        <v>3.937109589153632</v>
+      </c>
+      <c r="V82">
+        <v>8.246895061507445E-05</v>
+      </c>
+      <c r="Y82">
+        <v>1.929083492303374</v>
+      </c>
+      <c r="Z82">
+        <v>880.8076632166324</v>
+      </c>
+      <c r="AA82">
+        <v>0.0558724875989044</v>
+      </c>
+      <c r="AD82">
+        <v>0.02898360482091776</v>
+      </c>
+      <c r="AE82">
+        <v>0.08768723883412551</v>
+      </c>
+      <c r="AF82">
+        <v>0.1155953897232893</v>
+      </c>
+      <c r="AG82">
+        <v>0.004145194438372662</v>
+      </c>
+      <c r="AH82">
+        <v>0.122045497978154</v>
+      </c>
+      <c r="AI82">
+        <v>-0.0119301575738107</v>
+      </c>
+      <c r="AJ82">
+        <v>0.6538934426249396</v>
+      </c>
+      <c r="AK82">
+        <v>0.03892970025733097</v>
+      </c>
+      <c r="AL82">
+        <v>0.1753202809164403</v>
+      </c>
+      <c r="AM82">
+        <v>0.8228564066085329</v>
+      </c>
+    </row>
+    <row r="83" spans="1:39">
+      <c r="A83" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83" t="s">
+        <v>110</v>
+      </c>
+      <c r="C83" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" t="s">
+        <v>51</v>
+      </c>
+      <c r="H83">
+        <v>374</v>
+      </c>
+      <c r="I83" t="s">
+        <v>113</v>
+      </c>
+      <c r="J83" t="s">
+        <v>114</v>
+      </c>
+      <c r="K83" t="s">
+        <v>115</v>
+      </c>
+      <c r="L83" t="s">
+        <v>116</v>
+      </c>
+      <c r="M83">
+        <v>0.4325016405862215</v>
+      </c>
+      <c r="N83">
+        <v>0.1399244585755492</v>
+      </c>
+      <c r="O83">
+        <v>0.1582547412218785</v>
+      </c>
+      <c r="P83">
+        <v>0.7067485399505646</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>48</v>
+      </c>
+      <c r="R83">
+        <v>1.541108003611174</v>
+      </c>
+      <c r="S83">
+        <v>1.171464577018656</v>
+      </c>
+      <c r="T83">
+        <v>2.027388557355069</v>
+      </c>
+      <c r="U83">
+        <v>3.090965260749618</v>
+      </c>
+      <c r="V83">
+        <v>0.001995069737872486</v>
+      </c>
+      <c r="W83" t="s">
+        <v>49</v>
+      </c>
+      <c r="X83" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z83">
+        <v>872.2591700456863</v>
+      </c>
+      <c r="AA83">
+        <v>0.03130359421733797</v>
+      </c>
+      <c r="AB83">
+        <v>3.887948604422853</v>
+      </c>
+      <c r="AC83">
+        <v>0.7271111873200716</v>
+      </c>
+      <c r="AD83">
+        <v>0.02898360482091776</v>
+      </c>
+      <c r="AE83">
+        <v>0.08768723883412551</v>
+      </c>
+      <c r="AF83">
+        <v>0.1155953897232893</v>
+      </c>
+      <c r="AG83">
+        <v>0.004145194438372662</v>
+      </c>
+      <c r="AH83">
+        <v>0.122045497978154</v>
+      </c>
+      <c r="AI83">
+        <v>-0.0119301575738107</v>
+      </c>
+      <c r="AJ83">
+        <v>0.6538934426249396</v>
+      </c>
+      <c r="AK83">
+        <v>0.03892970025733097</v>
+      </c>
+      <c r="AL83">
+        <v>0.1753202809164403</v>
+      </c>
+      <c r="AM83">
+        <v>0.8228564066085329</v>
+      </c>
+    </row>
+    <row r="84" spans="1:39">
+      <c r="A84" t="s">
+        <v>147</v>
+      </c>
+      <c r="B84" t="s">
+        <v>120</v>
+      </c>
+      <c r="C84" t="s">
+        <v>130</v>
+      </c>
+      <c r="D84" t="s">
+        <v>50</v>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" t="s">
+        <v>51</v>
+      </c>
+      <c r="H84">
+        <v>374</v>
+      </c>
+      <c r="I84" t="s">
+        <v>121</v>
+      </c>
+      <c r="J84" t="s">
+        <v>122</v>
+      </c>
+      <c r="K84" t="s">
+        <v>123</v>
+      </c>
+      <c r="L84" t="s">
+        <v>124</v>
+      </c>
+      <c r="M84">
+        <v>-0.1688790605617998</v>
+      </c>
+      <c r="N84">
+        <v>0.04960088415735974</v>
+      </c>
+      <c r="O84">
+        <v>-0.2660950071115682</v>
+      </c>
+      <c r="P84">
+        <v>-0.07166311401203135</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>48</v>
+      </c>
+      <c r="R84">
+        <v>0.8446110439946544</v>
+      </c>
+      <c r="S84">
+        <v>0.7663663137922873</v>
+      </c>
+      <c r="T84">
+        <v>0.9308444314412914</v>
+      </c>
+      <c r="U84">
+        <v>-3.404759076996042</v>
+      </c>
+      <c r="V84">
+        <v>0.0006622245017961327</v>
+      </c>
+      <c r="W84" t="s">
+        <v>68</v>
+      </c>
+      <c r="X84" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z84">
+        <v>872.2591700456863</v>
+      </c>
+      <c r="AA84">
+        <v>0.03130359421733797</v>
+      </c>
+      <c r="AB84">
+        <v>3.887948604422853</v>
+      </c>
+      <c r="AC84">
+        <v>0.7271111873200716</v>
+      </c>
+      <c r="AD84">
+        <v>0.02898360482091776</v>
+      </c>
+      <c r="AE84">
+        <v>0.08768723883412551</v>
+      </c>
+      <c r="AF84">
+        <v>0.1155953897232893</v>
+      </c>
+      <c r="AG84">
+        <v>0.004145194438372662</v>
+      </c>
+      <c r="AH84">
+        <v>0.122045497978154</v>
+      </c>
+      <c r="AI84">
+        <v>-0.0119301575738107</v>
+      </c>
+      <c r="AJ84">
+        <v>0.6538934426249396</v>
+      </c>
+      <c r="AK84">
+        <v>0.03892970025733097</v>
+      </c>
+      <c r="AL84">
+        <v>0.1753202809164403</v>
+      </c>
+      <c r="AM84">
+        <v>0.8228564066085329</v>
+      </c>
+    </row>
+    <row r="85" spans="1:39">
+      <c r="A85" t="s">
+        <v>147</v>
+      </c>
+      <c r="B85" t="s">
+        <v>90</v>
+      </c>
+      <c r="C85" t="s">
+        <v>130</v>
+      </c>
+      <c r="D85" t="s">
+        <v>50</v>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" t="s">
+        <v>51</v>
+      </c>
+      <c r="H85">
+        <v>374</v>
+      </c>
+      <c r="I85" t="s">
+        <v>137</v>
+      </c>
+      <c r="J85" t="s">
+        <v>138</v>
+      </c>
+      <c r="K85" t="s">
+        <v>139</v>
+      </c>
+      <c r="L85" t="s">
+        <v>140</v>
+      </c>
+      <c r="M85">
+        <v>0.6232603279098032</v>
+      </c>
+      <c r="N85">
+        <v>0.1754988937168951</v>
+      </c>
+      <c r="O85">
+        <v>0.2792888168980662</v>
+      </c>
+      <c r="P85">
+        <v>0.9672318389215402</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>48</v>
+      </c>
+      <c r="R85">
+        <v>1.864998647528646</v>
+      </c>
+      <c r="S85">
+        <v>1.322189159301157</v>
+      </c>
+      <c r="T85">
+        <v>2.630652301764516</v>
+      </c>
+      <c r="U85">
+        <v>3.551363286170976</v>
+      </c>
+      <c r="V85">
+        <v>0.0003832410354328455</v>
+      </c>
+      <c r="Z85">
+        <v>872.2591700456863</v>
+      </c>
+      <c r="AA85">
+        <v>0.03130359421733797</v>
+      </c>
+      <c r="AB85">
+        <v>3.887948604422853</v>
+      </c>
+      <c r="AC85">
+        <v>0.7271111873200716</v>
+      </c>
+      <c r="AD85">
+        <v>0.02898360482091776</v>
+      </c>
+      <c r="AE85">
+        <v>0.08768723883412551</v>
+      </c>
+      <c r="AF85">
+        <v>0.1155953897232893</v>
+      </c>
+      <c r="AG85">
+        <v>0.004145194438372662</v>
+      </c>
+      <c r="AH85">
+        <v>0.122045497978154</v>
+      </c>
+      <c r="AI85">
+        <v>-0.0119301575738107</v>
+      </c>
+      <c r="AJ85">
+        <v>0.6538934426249396</v>
+      </c>
+      <c r="AK85">
+        <v>0.03892970025733097</v>
+      </c>
+      <c r="AL85">
+        <v>0.1753202809164403</v>
+      </c>
+      <c r="AM85">
+        <v>0.8228564066085329</v>
       </c>
     </row>
   </sheetData>

--- a/Outputs/Tables/model_results.xlsx
+++ b/Outputs/Tables/model_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="169">
   <si>
     <t>model_id</t>
   </si>
@@ -458,6 +458,69 @@
   </si>
   <si>
     <t>H10_H11_dens_sel</t>
+  </si>
+  <si>
+    <t>H7_spont</t>
+  </si>
+  <si>
+    <t>subset</t>
+  </si>
+  <si>
+    <t>Spontaneous count, visit 1</t>
+  </si>
+  <si>
+    <t>H7_prov</t>
+  </si>
+  <si>
+    <t>H8_spont</t>
+  </si>
+  <si>
+    <t>Spontaneous count, visit 2</t>
+  </si>
+  <si>
+    <t>H8_prov</t>
+  </si>
+  <si>
+    <t>H9_v1_class</t>
+  </si>
+  <si>
+    <t>loudness_class80-90</t>
+  </si>
+  <si>
+    <t>Device loudness 80–90 dB (vs &lt; 80 dB)</t>
+  </si>
+  <si>
+    <t>devices of 80–90 dB</t>
+  </si>
+  <si>
+    <t>vs &lt; 80 dB</t>
+  </si>
+  <si>
+    <t>loudness_class90-100</t>
+  </si>
+  <si>
+    <t>Device loudness 90–100 dB (vs &lt; 80 dB)</t>
+  </si>
+  <si>
+    <t>devices of 90–100 dB</t>
+  </si>
+  <si>
+    <t>loudness_class&gt;=100</t>
+  </si>
+  <si>
+    <t>Device loudness ≥ 100 dB (vs &lt; 80 dB)</t>
+  </si>
+  <si>
+    <t>devices of 100 dB or more</t>
+  </si>
+  <si>
+    <t>H9_v2_class</t>
+  </si>
+  <si>
+    <t>H10_H11_dens_selonly</t>
+  </si>
+  <si>
+    <t>H10_H11_dens_selonly_lowcal</t>
   </si>
 </sst>
 </file>
@@ -800,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM85"/>
+  <dimension ref="A1:AM109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:39" s="1" customFormat="1">
@@ -10144,6 +10207,2424 @@
         <v>0.8228564066085329</v>
       </c>
     </row>
+    <row r="86" spans="1:39">
+      <c r="A86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B86" t="s">
+        <v>77</v>
+      </c>
+      <c r="C86" t="s">
+        <v>149</v>
+      </c>
+      <c r="D86" t="s">
+        <v>41</v>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="s">
+        <v>150</v>
+      </c>
+      <c r="G86" t="s">
+        <v>43</v>
+      </c>
+      <c r="H86">
+        <v>362</v>
+      </c>
+      <c r="I86" t="s">
+        <v>79</v>
+      </c>
+      <c r="J86" t="s">
+        <v>80</v>
+      </c>
+      <c r="K86" t="s">
+        <v>81</v>
+      </c>
+      <c r="L86" t="s">
+        <v>82</v>
+      </c>
+      <c r="M86">
+        <v>-0.2088554237632885</v>
+      </c>
+      <c r="N86">
+        <v>0.09779084741077615</v>
+      </c>
+      <c r="O86">
+        <v>-0.4005219627060618</v>
+      </c>
+      <c r="P86">
+        <v>-0.01718888482051531</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>48</v>
+      </c>
+      <c r="R86">
+        <v>0.8115125525934835</v>
+      </c>
+      <c r="S86">
+        <v>0.6699702552672927</v>
+      </c>
+      <c r="T86">
+        <v>0.9829580012534348</v>
+      </c>
+      <c r="U86">
+        <v>-2.135735902624702</v>
+      </c>
+      <c r="V86">
+        <v>0.03270094625792737</v>
+      </c>
+      <c r="W86" t="s">
+        <v>83</v>
+      </c>
+      <c r="X86" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y86">
+        <v>0.4178054304821218</v>
+      </c>
+      <c r="Z86">
+        <v>343.6368381376739</v>
+      </c>
+      <c r="AA86">
+        <v>0.01348136608387085</v>
+      </c>
+      <c r="AD86">
+        <v>-0.01692473162528257</v>
+      </c>
+      <c r="AE86">
+        <v>0.7244576351878997</v>
+      </c>
+      <c r="AF86">
+        <v>-0.0343128220471781</v>
+      </c>
+      <c r="AG86">
+        <v>0.746210819363994</v>
+      </c>
+      <c r="AH86">
+        <v>0.9965384836384295</v>
+      </c>
+    </row>
+    <row r="87" spans="1:39">
+      <c r="A87" t="s">
+        <v>151</v>
+      </c>
+      <c r="B87" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" t="s">
+        <v>149</v>
+      </c>
+      <c r="D87" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" t="s">
+        <v>101</v>
+      </c>
+      <c r="G87" t="s">
+        <v>43</v>
+      </c>
+      <c r="H87">
+        <v>361</v>
+      </c>
+      <c r="I87" t="s">
+        <v>79</v>
+      </c>
+      <c r="J87" t="s">
+        <v>80</v>
+      </c>
+      <c r="K87" t="s">
+        <v>81</v>
+      </c>
+      <c r="L87" t="s">
+        <v>82</v>
+      </c>
+      <c r="M87">
+        <v>-0.2552815108724086</v>
+      </c>
+      <c r="N87">
+        <v>0.0690673713296034</v>
+      </c>
+      <c r="O87">
+        <v>-0.3906510711852856</v>
+      </c>
+      <c r="P87">
+        <v>-0.1199119505595317</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>48</v>
+      </c>
+      <c r="R87">
+        <v>0.7746983812442502</v>
+      </c>
+      <c r="S87">
+        <v>0.6766162057453095</v>
+      </c>
+      <c r="T87">
+        <v>0.8869985330034671</v>
+      </c>
+      <c r="U87">
+        <v>-3.696123161458598</v>
+      </c>
+      <c r="V87">
+        <v>0.0002189168032810251</v>
+      </c>
+      <c r="W87" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y87">
+        <v>0.8073246442375696</v>
+      </c>
+      <c r="Z87">
+        <v>605.4003700524531</v>
+      </c>
+      <c r="AA87">
+        <v>0.02281027888795328</v>
+      </c>
+      <c r="AD87">
+        <v>0.04380605359686635</v>
+      </c>
+      <c r="AE87">
+        <v>0.02503613505867666</v>
+      </c>
+      <c r="AF87">
+        <v>0.07946400378379827</v>
+      </c>
+      <c r="AG87">
+        <v>0.03944389615720765</v>
+      </c>
+      <c r="AH87">
+        <v>0.0002702145147677193</v>
+      </c>
+      <c r="AI87">
+        <v>-0.02462231244713045</v>
+      </c>
+      <c r="AJ87">
+        <v>0.8208617609151636</v>
+      </c>
+      <c r="AK87">
+        <v>0.01287173401239563</v>
+      </c>
+      <c r="AL87">
+        <v>0.3668818456876382</v>
+      </c>
+      <c r="AM87">
+        <v>0.640289330391089</v>
+      </c>
+    </row>
+    <row r="88" spans="1:39">
+      <c r="A88" t="s">
+        <v>151</v>
+      </c>
+      <c r="B88" t="s">
+        <v>77</v>
+      </c>
+      <c r="C88" t="s">
+        <v>149</v>
+      </c>
+      <c r="D88" t="s">
+        <v>50</v>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>101</v>
+      </c>
+      <c r="G88" t="s">
+        <v>133</v>
+      </c>
+      <c r="H88">
+        <v>361</v>
+      </c>
+      <c r="I88" t="s">
+        <v>79</v>
+      </c>
+      <c r="J88" t="s">
+        <v>80</v>
+      </c>
+      <c r="K88" t="s">
+        <v>81</v>
+      </c>
+      <c r="L88" t="s">
+        <v>82</v>
+      </c>
+      <c r="M88">
+        <v>-0.2805661320636845</v>
+      </c>
+      <c r="N88">
+        <v>0.06846467710639124</v>
+      </c>
+      <c r="O88">
+        <v>-0.4147544334053753</v>
+      </c>
+      <c r="P88">
+        <v>-0.1463778307219938</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>48</v>
+      </c>
+      <c r="R88">
+        <v>0.7553559891400513</v>
+      </c>
+      <c r="S88">
+        <v>0.6605024581308733</v>
+      </c>
+      <c r="T88">
+        <v>0.8638312595298364</v>
+      </c>
+      <c r="U88">
+        <v>-4.097969112272252</v>
+      </c>
+      <c r="V88">
+        <v>4.167908803745006E-05</v>
+      </c>
+      <c r="W88" t="s">
+        <v>83</v>
+      </c>
+      <c r="X88" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y88">
+        <v>0.8073246442375696</v>
+      </c>
+      <c r="Z88">
+        <v>587.6867960920654</v>
+      </c>
+      <c r="AA88">
+        <v>0.02677289318673459</v>
+      </c>
+      <c r="AB88">
+        <v>260.135697419514</v>
+      </c>
+      <c r="AC88">
+        <v>0.8121735641837692</v>
+      </c>
+      <c r="AD88">
+        <v>0.04380605359686635</v>
+      </c>
+      <c r="AE88">
+        <v>0.02503613505867666</v>
+      </c>
+      <c r="AF88">
+        <v>0.07946400378379827</v>
+      </c>
+      <c r="AG88">
+        <v>0.03944389615720765</v>
+      </c>
+      <c r="AH88">
+        <v>0.0002702145147677193</v>
+      </c>
+      <c r="AI88">
+        <v>-0.02462231244713045</v>
+      </c>
+      <c r="AJ88">
+        <v>0.8208617609151636</v>
+      </c>
+      <c r="AK88">
+        <v>0.01287173401239563</v>
+      </c>
+      <c r="AL88">
+        <v>0.3668818456876382</v>
+      </c>
+      <c r="AM88">
+        <v>0.640289330391089</v>
+      </c>
+    </row>
+    <row r="89" spans="1:39">
+      <c r="A89" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" t="s">
+        <v>85</v>
+      </c>
+      <c r="C89" t="s">
+        <v>149</v>
+      </c>
+      <c r="D89" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+      <c r="F89" t="s">
+        <v>153</v>
+      </c>
+      <c r="G89" t="s">
+        <v>43</v>
+      </c>
+      <c r="H89">
+        <v>354</v>
+      </c>
+      <c r="I89" t="s">
+        <v>87</v>
+      </c>
+      <c r="J89" t="s">
+        <v>88</v>
+      </c>
+      <c r="K89" t="s">
+        <v>89</v>
+      </c>
+      <c r="L89" t="s">
+        <v>82</v>
+      </c>
+      <c r="M89">
+        <v>0.2278021706401877</v>
+      </c>
+      <c r="N89">
+        <v>0.1185035248746196</v>
+      </c>
+      <c r="O89">
+        <v>-0.004460470155113139</v>
+      </c>
+      <c r="P89">
+        <v>0.4600648114354884</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>48</v>
+      </c>
+      <c r="R89">
+        <v>1.255836859454287</v>
+      </c>
+      <c r="S89">
+        <v>0.9955494629676021</v>
+      </c>
+      <c r="T89">
+        <v>1.58417665443041</v>
+      </c>
+      <c r="U89">
+        <v>1.922324005815096</v>
+      </c>
+      <c r="V89">
+        <v>0.05456500119478824</v>
+      </c>
+      <c r="W89" t="s">
+        <v>83</v>
+      </c>
+      <c r="X89" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y89">
+        <v>0.5811539804444464</v>
+      </c>
+      <c r="Z89">
+        <v>331.9086412875165</v>
+      </c>
+      <c r="AA89">
+        <v>0.03099809921225616</v>
+      </c>
+      <c r="AD89">
+        <v>-0.01962586642447821</v>
+      </c>
+      <c r="AE89">
+        <v>0.757921675728828</v>
+      </c>
+      <c r="AF89">
+        <v>0.02310477793664775</v>
+      </c>
+      <c r="AG89">
+        <v>0.2889220518073117</v>
+      </c>
+      <c r="AH89">
+        <v>0.7680579011322347</v>
+      </c>
+    </row>
+    <row r="90" spans="1:39">
+      <c r="A90" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" t="s">
+        <v>90</v>
+      </c>
+      <c r="C90" t="s">
+        <v>149</v>
+      </c>
+      <c r="D90" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>153</v>
+      </c>
+      <c r="G90" t="s">
+        <v>43</v>
+      </c>
+      <c r="H90">
+        <v>354</v>
+      </c>
+      <c r="I90" t="s">
+        <v>91</v>
+      </c>
+      <c r="J90" t="s">
+        <v>92</v>
+      </c>
+      <c r="K90" t="s">
+        <v>93</v>
+      </c>
+      <c r="L90" t="s">
+        <v>94</v>
+      </c>
+      <c r="M90">
+        <v>-0.8897890231459847</v>
+      </c>
+      <c r="N90">
+        <v>0.4431778711812006</v>
+      </c>
+      <c r="O90">
+        <v>-1.758401689406269</v>
+      </c>
+      <c r="P90">
+        <v>-0.02117635688570019</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>48</v>
+      </c>
+      <c r="R90">
+        <v>0.4107424007511841</v>
+      </c>
+      <c r="S90">
+        <v>0.1723200648212456</v>
+      </c>
+      <c r="T90">
+        <v>0.9790462877892667</v>
+      </c>
+      <c r="U90">
+        <v>-2.007746958968039</v>
+      </c>
+      <c r="V90">
+        <v>0.04467018779808658</v>
+      </c>
+      <c r="Y90">
+        <v>0.5811539804444464</v>
+      </c>
+      <c r="Z90">
+        <v>331.9086412875165</v>
+      </c>
+      <c r="AA90">
+        <v>0.03099809921225616</v>
+      </c>
+      <c r="AD90">
+        <v>-0.01962586642447821</v>
+      </c>
+      <c r="AE90">
+        <v>0.757921675728828</v>
+      </c>
+      <c r="AF90">
+        <v>0.02310477793664775</v>
+      </c>
+      <c r="AG90">
+        <v>0.2889220518073117</v>
+      </c>
+      <c r="AH90">
+        <v>0.7680579011322347</v>
+      </c>
+    </row>
+    <row r="91" spans="1:39">
+      <c r="A91" t="s">
+        <v>152</v>
+      </c>
+      <c r="B91" t="s">
+        <v>90</v>
+      </c>
+      <c r="C91" t="s">
+        <v>149</v>
+      </c>
+      <c r="D91" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" t="s">
+        <v>153</v>
+      </c>
+      <c r="G91" t="s">
+        <v>43</v>
+      </c>
+      <c r="H91">
+        <v>354</v>
+      </c>
+      <c r="I91" t="s">
+        <v>95</v>
+      </c>
+      <c r="J91" t="s">
+        <v>96</v>
+      </c>
+      <c r="K91" t="s">
+        <v>97</v>
+      </c>
+      <c r="L91" t="s">
+        <v>94</v>
+      </c>
+      <c r="M91">
+        <v>1.196772725503205</v>
+      </c>
+      <c r="N91">
+        <v>0.78141282463241</v>
+      </c>
+      <c r="O91">
+        <v>-0.3347682678340311</v>
+      </c>
+      <c r="P91">
+        <v>2.728313718840442</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>48</v>
+      </c>
+      <c r="R91">
+        <v>3.309419265488571</v>
+      </c>
+      <c r="S91">
+        <v>0.7155038724049491</v>
+      </c>
+      <c r="T91">
+        <v>15.30705324902608</v>
+      </c>
+      <c r="U91">
+        <v>1.531549889862875</v>
+      </c>
+      <c r="V91">
+        <v>0.1256335462018899</v>
+      </c>
+      <c r="Y91">
+        <v>0.5811539804444464</v>
+      </c>
+      <c r="Z91">
+        <v>331.9086412875165</v>
+      </c>
+      <c r="AA91">
+        <v>0.03099809921225616</v>
+      </c>
+      <c r="AD91">
+        <v>-0.01962586642447821</v>
+      </c>
+      <c r="AE91">
+        <v>0.757921675728828</v>
+      </c>
+      <c r="AF91">
+        <v>0.02310477793664775</v>
+      </c>
+      <c r="AG91">
+        <v>0.2889220518073117</v>
+      </c>
+      <c r="AH91">
+        <v>0.7680579011322347</v>
+      </c>
+    </row>
+    <row r="92" spans="1:39">
+      <c r="A92" t="s">
+        <v>154</v>
+      </c>
+      <c r="B92" t="s">
+        <v>85</v>
+      </c>
+      <c r="C92" t="s">
+        <v>149</v>
+      </c>
+      <c r="D92" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" t="s">
+        <v>107</v>
+      </c>
+      <c r="G92" t="s">
+        <v>43</v>
+      </c>
+      <c r="H92">
+        <v>354</v>
+      </c>
+      <c r="I92" t="s">
+        <v>87</v>
+      </c>
+      <c r="J92" t="s">
+        <v>88</v>
+      </c>
+      <c r="K92" t="s">
+        <v>89</v>
+      </c>
+      <c r="L92" t="s">
+        <v>82</v>
+      </c>
+      <c r="M92">
+        <v>-0.02594997392866997</v>
+      </c>
+      <c r="N92">
+        <v>0.071135629884542</v>
+      </c>
+      <c r="O92">
+        <v>-0.1653732465199434</v>
+      </c>
+      <c r="P92">
+        <v>0.1134732986626035</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>48</v>
+      </c>
+      <c r="R92">
+        <v>0.974383832984651</v>
+      </c>
+      <c r="S92">
+        <v>0.8475772897675284</v>
+      </c>
+      <c r="T92">
+        <v>1.12016197867013</v>
+      </c>
+      <c r="U92">
+        <v>-0.3647957285370012</v>
+      </c>
+      <c r="V92">
+        <v>0.7152638938383014</v>
+      </c>
+      <c r="W92" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y92">
+        <v>1.47212996434032</v>
+      </c>
+      <c r="Z92">
+        <v>609.9411060192901</v>
+      </c>
+      <c r="AA92">
+        <v>0.002872421971886752</v>
+      </c>
+      <c r="AD92">
+        <v>0.06279222907713251</v>
+      </c>
+      <c r="AE92">
+        <v>0.003130964596513673</v>
+      </c>
+      <c r="AF92">
+        <v>0.08911545059792679</v>
+      </c>
+      <c r="AG92">
+        <v>0.02533783719221571</v>
+      </c>
+      <c r="AH92">
+        <v>0.0002418776573451797</v>
+      </c>
+      <c r="AI92">
+        <v>-0.009214017199138107</v>
+      </c>
+      <c r="AJ92">
+        <v>0.6048136069684058</v>
+      </c>
+      <c r="AK92">
+        <v>-0.01903187605963569</v>
+      </c>
+      <c r="AL92">
+        <v>0.6314828734756739</v>
+      </c>
+      <c r="AM92">
+        <v>0.3027195787835912</v>
+      </c>
+    </row>
+    <row r="93" spans="1:39">
+      <c r="A93" t="s">
+        <v>154</v>
+      </c>
+      <c r="B93" t="s">
+        <v>90</v>
+      </c>
+      <c r="C93" t="s">
+        <v>149</v>
+      </c>
+      <c r="D93" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" t="s">
+        <v>107</v>
+      </c>
+      <c r="G93" t="s">
+        <v>43</v>
+      </c>
+      <c r="H93">
+        <v>354</v>
+      </c>
+      <c r="I93" t="s">
+        <v>91</v>
+      </c>
+      <c r="J93" t="s">
+        <v>92</v>
+      </c>
+      <c r="K93" t="s">
+        <v>93</v>
+      </c>
+      <c r="L93" t="s">
+        <v>94</v>
+      </c>
+      <c r="M93">
+        <v>0.2638673268239927</v>
+      </c>
+      <c r="N93">
+        <v>0.2083313688377325</v>
+      </c>
+      <c r="O93">
+        <v>-0.1444546529478929</v>
+      </c>
+      <c r="P93">
+        <v>0.6721893065958784</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>48</v>
+      </c>
+      <c r="R93">
+        <v>1.301955450277158</v>
+      </c>
+      <c r="S93">
+        <v>0.8654941591219707</v>
+      </c>
+      <c r="T93">
+        <v>1.958520432103244</v>
+      </c>
+      <c r="U93">
+        <v>1.266575112025097</v>
+      </c>
+      <c r="V93">
+        <v>0.2053072561997599</v>
+      </c>
+      <c r="Y93">
+        <v>1.47212996434032</v>
+      </c>
+      <c r="Z93">
+        <v>609.9411060192901</v>
+      </c>
+      <c r="AA93">
+        <v>0.002872421971886752</v>
+      </c>
+      <c r="AD93">
+        <v>0.06279222907713251</v>
+      </c>
+      <c r="AE93">
+        <v>0.003130964596513673</v>
+      </c>
+      <c r="AF93">
+        <v>0.08911545059792679</v>
+      </c>
+      <c r="AG93">
+        <v>0.02533783719221571</v>
+      </c>
+      <c r="AH93">
+        <v>0.0002418776573451797</v>
+      </c>
+      <c r="AI93">
+        <v>-0.009214017199138107</v>
+      </c>
+      <c r="AJ93">
+        <v>0.6048136069684058</v>
+      </c>
+      <c r="AK93">
+        <v>-0.01903187605963569</v>
+      </c>
+      <c r="AL93">
+        <v>0.6314828734756739</v>
+      </c>
+      <c r="AM93">
+        <v>0.3027195787835912</v>
+      </c>
+    </row>
+    <row r="94" spans="1:39">
+      <c r="A94" t="s">
+        <v>154</v>
+      </c>
+      <c r="B94" t="s">
+        <v>90</v>
+      </c>
+      <c r="C94" t="s">
+        <v>149</v>
+      </c>
+      <c r="D94" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94" t="b">
+        <v>0</v>
+      </c>
+      <c r="F94" t="s">
+        <v>107</v>
+      </c>
+      <c r="G94" t="s">
+        <v>43</v>
+      </c>
+      <c r="H94">
+        <v>354</v>
+      </c>
+      <c r="I94" t="s">
+        <v>95</v>
+      </c>
+      <c r="J94" t="s">
+        <v>96</v>
+      </c>
+      <c r="K94" t="s">
+        <v>97</v>
+      </c>
+      <c r="L94" t="s">
+        <v>94</v>
+      </c>
+      <c r="M94">
+        <v>0.2866787909467804</v>
+      </c>
+      <c r="N94">
+        <v>0.6186263489458452</v>
+      </c>
+      <c r="O94">
+        <v>-0.925806572874584</v>
+      </c>
+      <c r="P94">
+        <v>1.499164154768145</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>48</v>
+      </c>
+      <c r="R94">
+        <v>1.331996295484824</v>
+      </c>
+      <c r="S94">
+        <v>0.3962117165374762</v>
+      </c>
+      <c r="T94">
+        <v>4.477944636999342</v>
+      </c>
+      <c r="U94">
+        <v>0.4634118663637399</v>
+      </c>
+      <c r="V94">
+        <v>0.6430691745964943</v>
+      </c>
+      <c r="Y94">
+        <v>1.47212996434032</v>
+      </c>
+      <c r="Z94">
+        <v>609.9411060192901</v>
+      </c>
+      <c r="AA94">
+        <v>0.002872421971886752</v>
+      </c>
+      <c r="AD94">
+        <v>0.06279222907713251</v>
+      </c>
+      <c r="AE94">
+        <v>0.003130964596513673</v>
+      </c>
+      <c r="AF94">
+        <v>0.08911545059792679</v>
+      </c>
+      <c r="AG94">
+        <v>0.02533783719221571</v>
+      </c>
+      <c r="AH94">
+        <v>0.0002418776573451797</v>
+      </c>
+      <c r="AI94">
+        <v>-0.009214017199138107</v>
+      </c>
+      <c r="AJ94">
+        <v>0.6048136069684058</v>
+      </c>
+      <c r="AK94">
+        <v>-0.01903187605963569</v>
+      </c>
+      <c r="AL94">
+        <v>0.6314828734756739</v>
+      </c>
+      <c r="AM94">
+        <v>0.3027195787835912</v>
+      </c>
+    </row>
+    <row r="95" spans="1:39">
+      <c r="A95" t="s">
+        <v>154</v>
+      </c>
+      <c r="B95" t="s">
+        <v>85</v>
+      </c>
+      <c r="C95" t="s">
+        <v>149</v>
+      </c>
+      <c r="D95" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>107</v>
+      </c>
+      <c r="G95" t="s">
+        <v>51</v>
+      </c>
+      <c r="H95">
+        <v>354</v>
+      </c>
+      <c r="I95" t="s">
+        <v>87</v>
+      </c>
+      <c r="J95" t="s">
+        <v>88</v>
+      </c>
+      <c r="K95" t="s">
+        <v>89</v>
+      </c>
+      <c r="L95" t="s">
+        <v>82</v>
+      </c>
+      <c r="M95">
+        <v>-0.04583810019367455</v>
+      </c>
+      <c r="N95">
+        <v>0.07567974050219441</v>
+      </c>
+      <c r="O95">
+        <v>-0.1941676659373128</v>
+      </c>
+      <c r="P95">
+        <v>0.1024914655499637</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>48</v>
+      </c>
+      <c r="R95">
+        <v>0.9551965958166653</v>
+      </c>
+      <c r="S95">
+        <v>0.8235198164706661</v>
+      </c>
+      <c r="T95">
+        <v>1.107927846314607</v>
+      </c>
+      <c r="U95">
+        <v>-0.6056852189172799</v>
+      </c>
+      <c r="V95">
+        <v>0.5447238011190841</v>
+      </c>
+      <c r="W95" t="s">
+        <v>83</v>
+      </c>
+      <c r="X95" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z95">
+        <v>590.1943882673806</v>
+      </c>
+      <c r="AA95">
+        <v>0.003458868848606245</v>
+      </c>
+      <c r="AB95">
+        <v>14.4786245108509</v>
+      </c>
+      <c r="AC95">
+        <v>0.8435062336650891</v>
+      </c>
+      <c r="AD95">
+        <v>0.06279222907713251</v>
+      </c>
+      <c r="AE95">
+        <v>0.003130964596513673</v>
+      </c>
+      <c r="AF95">
+        <v>0.08911545059792679</v>
+      </c>
+      <c r="AG95">
+        <v>0.02533783719221571</v>
+      </c>
+      <c r="AH95">
+        <v>0.0002418776573451797</v>
+      </c>
+      <c r="AI95">
+        <v>-0.009214017199138107</v>
+      </c>
+      <c r="AJ95">
+        <v>0.6048136069684058</v>
+      </c>
+      <c r="AK95">
+        <v>-0.01903187605963569</v>
+      </c>
+      <c r="AL95">
+        <v>0.6314828734756739</v>
+      </c>
+      <c r="AM95">
+        <v>0.3027195787835912</v>
+      </c>
+    </row>
+    <row r="96" spans="1:39">
+      <c r="A96" t="s">
+        <v>154</v>
+      </c>
+      <c r="B96" t="s">
+        <v>90</v>
+      </c>
+      <c r="C96" t="s">
+        <v>149</v>
+      </c>
+      <c r="D96" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>107</v>
+      </c>
+      <c r="G96" t="s">
+        <v>51</v>
+      </c>
+      <c r="H96">
+        <v>354</v>
+      </c>
+      <c r="I96" t="s">
+        <v>91</v>
+      </c>
+      <c r="J96" t="s">
+        <v>92</v>
+      </c>
+      <c r="K96" t="s">
+        <v>93</v>
+      </c>
+      <c r="L96" t="s">
+        <v>94</v>
+      </c>
+      <c r="M96">
+        <v>0.1624220401044004</v>
+      </c>
+      <c r="N96">
+        <v>0.2231800658671059</v>
+      </c>
+      <c r="O96">
+        <v>-0.2750028510624042</v>
+      </c>
+      <c r="P96">
+        <v>0.5998469312712049</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>48</v>
+      </c>
+      <c r="R96">
+        <v>1.17635660623559</v>
+      </c>
+      <c r="S96">
+        <v>0.7595699576405318</v>
+      </c>
+      <c r="T96">
+        <v>1.821839912327085</v>
+      </c>
+      <c r="U96">
+        <v>0.7277623092069329</v>
+      </c>
+      <c r="V96">
+        <v>0.4667591005103527</v>
+      </c>
+      <c r="Z96">
+        <v>590.1943882673806</v>
+      </c>
+      <c r="AA96">
+        <v>0.003458868848606245</v>
+      </c>
+      <c r="AB96">
+        <v>14.4786245108509</v>
+      </c>
+      <c r="AC96">
+        <v>0.8435062336650891</v>
+      </c>
+      <c r="AD96">
+        <v>0.06279222907713251</v>
+      </c>
+      <c r="AE96">
+        <v>0.003130964596513673</v>
+      </c>
+      <c r="AF96">
+        <v>0.08911545059792679</v>
+      </c>
+      <c r="AG96">
+        <v>0.02533783719221571</v>
+      </c>
+      <c r="AH96">
+        <v>0.0002418776573451797</v>
+      </c>
+      <c r="AI96">
+        <v>-0.009214017199138107</v>
+      </c>
+      <c r="AJ96">
+        <v>0.6048136069684058</v>
+      </c>
+      <c r="AK96">
+        <v>-0.01903187605963569</v>
+      </c>
+      <c r="AL96">
+        <v>0.6314828734756739</v>
+      </c>
+      <c r="AM96">
+        <v>0.3027195787835912</v>
+      </c>
+    </row>
+    <row r="97" spans="1:39">
+      <c r="A97" t="s">
+        <v>154</v>
+      </c>
+      <c r="B97" t="s">
+        <v>90</v>
+      </c>
+      <c r="C97" t="s">
+        <v>149</v>
+      </c>
+      <c r="D97" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>107</v>
+      </c>
+      <c r="G97" t="s">
+        <v>51</v>
+      </c>
+      <c r="H97">
+        <v>354</v>
+      </c>
+      <c r="I97" t="s">
+        <v>95</v>
+      </c>
+      <c r="J97" t="s">
+        <v>96</v>
+      </c>
+      <c r="K97" t="s">
+        <v>97</v>
+      </c>
+      <c r="L97" t="s">
+        <v>94</v>
+      </c>
+      <c r="M97">
+        <v>0.7849404605872226</v>
+      </c>
+      <c r="N97">
+        <v>0.6327445103324674</v>
+      </c>
+      <c r="O97">
+        <v>-0.4552159910798452</v>
+      </c>
+      <c r="P97">
+        <v>2.02509691225429</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>48</v>
+      </c>
+      <c r="R97">
+        <v>2.192276409997295</v>
+      </c>
+      <c r="S97">
+        <v>0.6343109476446398</v>
+      </c>
+      <c r="T97">
+        <v>7.576845198205754</v>
+      </c>
+      <c r="U97">
+        <v>1.24053302362874</v>
+      </c>
+      <c r="V97">
+        <v>0.2147783074166748</v>
+      </c>
+      <c r="Z97">
+        <v>590.1943882673806</v>
+      </c>
+      <c r="AA97">
+        <v>0.003458868848606245</v>
+      </c>
+      <c r="AB97">
+        <v>14.4786245108509</v>
+      </c>
+      <c r="AC97">
+        <v>0.8435062336650891</v>
+      </c>
+      <c r="AD97">
+        <v>0.06279222907713251</v>
+      </c>
+      <c r="AE97">
+        <v>0.003130964596513673</v>
+      </c>
+      <c r="AF97">
+        <v>0.08911545059792679</v>
+      </c>
+      <c r="AG97">
+        <v>0.02533783719221571</v>
+      </c>
+      <c r="AH97">
+        <v>0.0002418776573451797</v>
+      </c>
+      <c r="AI97">
+        <v>-0.009214017199138107</v>
+      </c>
+      <c r="AJ97">
+        <v>0.6048136069684058</v>
+      </c>
+      <c r="AK97">
+        <v>-0.01903187605963569</v>
+      </c>
+      <c r="AL97">
+        <v>0.6314828734756739</v>
+      </c>
+      <c r="AM97">
+        <v>0.3027195787835912</v>
+      </c>
+    </row>
+    <row r="98" spans="1:39">
+      <c r="A98" t="s">
+        <v>155</v>
+      </c>
+      <c r="B98" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" t="s">
+        <v>149</v>
+      </c>
+      <c r="D98" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98" t="b">
+        <v>1</v>
+      </c>
+      <c r="F98" t="s">
+        <v>101</v>
+      </c>
+      <c r="G98" t="s">
+        <v>43</v>
+      </c>
+      <c r="H98">
+        <v>374</v>
+      </c>
+      <c r="I98" t="s">
+        <v>156</v>
+      </c>
+      <c r="J98" t="s">
+        <v>157</v>
+      </c>
+      <c r="K98" t="s">
+        <v>158</v>
+      </c>
+      <c r="L98" t="s">
+        <v>159</v>
+      </c>
+      <c r="M98">
+        <v>0.5362889187684159</v>
+      </c>
+      <c r="N98">
+        <v>0.3518360020097002</v>
+      </c>
+      <c r="O98">
+        <v>-0.1532969736351585</v>
+      </c>
+      <c r="P98">
+        <v>1.22587481117199</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>48</v>
+      </c>
+      <c r="R98">
+        <v>1.709650423251085</v>
+      </c>
+      <c r="S98">
+        <v>0.8578749177453875</v>
+      </c>
+      <c r="T98">
+        <v>3.407145388286216</v>
+      </c>
+      <c r="U98">
+        <v>1.52425822174284</v>
+      </c>
+      <c r="V98">
+        <v>0.1274442191029556</v>
+      </c>
+      <c r="W98" t="s">
+        <v>49</v>
+      </c>
+      <c r="X98" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y98">
+        <v>1.756930293317255</v>
+      </c>
+      <c r="Z98">
+        <v>630.1717340608834</v>
+      </c>
+      <c r="AA98">
+        <v>0.01264958433481189</v>
+      </c>
+      <c r="AD98">
+        <v>0.0002674869681268992</v>
+      </c>
+      <c r="AE98">
+        <v>0.4498676132664657</v>
+      </c>
+      <c r="AF98">
+        <v>-0.01008496105843576</v>
+      </c>
+      <c r="AG98">
+        <v>0.5618393027158205</v>
+      </c>
+      <c r="AH98">
+        <v>0.7296574749189193</v>
+      </c>
+    </row>
+    <row r="99" spans="1:39">
+      <c r="A99" t="s">
+        <v>155</v>
+      </c>
+      <c r="B99" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99" t="s">
+        <v>149</v>
+      </c>
+      <c r="D99" t="s">
+        <v>41</v>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+      <c r="F99" t="s">
+        <v>101</v>
+      </c>
+      <c r="G99" t="s">
+        <v>43</v>
+      </c>
+      <c r="H99">
+        <v>374</v>
+      </c>
+      <c r="I99" t="s">
+        <v>160</v>
+      </c>
+      <c r="J99" t="s">
+        <v>161</v>
+      </c>
+      <c r="K99" t="s">
+        <v>162</v>
+      </c>
+      <c r="L99" t="s">
+        <v>159</v>
+      </c>
+      <c r="M99">
+        <v>0.8108087535731383</v>
+      </c>
+      <c r="N99">
+        <v>0.4495394725355707</v>
+      </c>
+      <c r="O99">
+        <v>-0.07027242222571284</v>
+      </c>
+      <c r="P99">
+        <v>1.691889929371989</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>48</v>
+      </c>
+      <c r="R99">
+        <v>2.24972672564947</v>
+      </c>
+      <c r="S99">
+        <v>0.9321398497014234</v>
+      </c>
+      <c r="T99">
+        <v>5.429732825737121</v>
+      </c>
+      <c r="U99">
+        <v>1.803643068315834</v>
+      </c>
+      <c r="V99">
+        <v>0.07128727981577819</v>
+      </c>
+      <c r="W99" t="s">
+        <v>49</v>
+      </c>
+      <c r="X99" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y99">
+        <v>1.756930293317255</v>
+      </c>
+      <c r="Z99">
+        <v>630.1717340608834</v>
+      </c>
+      <c r="AA99">
+        <v>0.01264958433481189</v>
+      </c>
+      <c r="AD99">
+        <v>0.0002674869681268992</v>
+      </c>
+      <c r="AE99">
+        <v>0.4498676132664657</v>
+      </c>
+      <c r="AF99">
+        <v>-0.01008496105843576</v>
+      </c>
+      <c r="AG99">
+        <v>0.5618393027158205</v>
+      </c>
+      <c r="AH99">
+        <v>0.7296574749189193</v>
+      </c>
+    </row>
+    <row r="100" spans="1:39">
+      <c r="A100" t="s">
+        <v>155</v>
+      </c>
+      <c r="B100" t="s">
+        <v>100</v>
+      </c>
+      <c r="C100" t="s">
+        <v>149</v>
+      </c>
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
+        <v>101</v>
+      </c>
+      <c r="G100" t="s">
+        <v>43</v>
+      </c>
+      <c r="H100">
+        <v>374</v>
+      </c>
+      <c r="I100" t="s">
+        <v>163</v>
+      </c>
+      <c r="J100" t="s">
+        <v>164</v>
+      </c>
+      <c r="K100" t="s">
+        <v>165</v>
+      </c>
+      <c r="L100" t="s">
+        <v>159</v>
+      </c>
+      <c r="M100">
+        <v>1.917115479880704</v>
+      </c>
+      <c r="N100">
+        <v>0.6820965625152101</v>
+      </c>
+      <c r="O100">
+        <v>0.5802307833723186</v>
+      </c>
+      <c r="P100">
+        <v>3.254000176389089</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>48</v>
+      </c>
+      <c r="R100">
+        <v>6.801311626831928</v>
+      </c>
+      <c r="S100">
+        <v>1.786450666288937</v>
+      </c>
+      <c r="T100">
+        <v>25.89371244232138</v>
+      </c>
+      <c r="U100">
+        <v>2.810621816962981</v>
+      </c>
+      <c r="V100">
+        <v>0.004944586716896902</v>
+      </c>
+      <c r="W100" t="s">
+        <v>49</v>
+      </c>
+      <c r="X100" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y100">
+        <v>1.756930293317255</v>
+      </c>
+      <c r="Z100">
+        <v>630.1717340608834</v>
+      </c>
+      <c r="AA100">
+        <v>0.01264958433481189</v>
+      </c>
+      <c r="AD100">
+        <v>0.0002674869681268992</v>
+      </c>
+      <c r="AE100">
+        <v>0.4498676132664657</v>
+      </c>
+      <c r="AF100">
+        <v>-0.01008496105843576</v>
+      </c>
+      <c r="AG100">
+        <v>0.5618393027158205</v>
+      </c>
+      <c r="AH100">
+        <v>0.7296574749189193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:39">
+      <c r="A101" t="s">
+        <v>166</v>
+      </c>
+      <c r="B101" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" t="s">
+        <v>149</v>
+      </c>
+      <c r="D101" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>107</v>
+      </c>
+      <c r="G101" t="s">
+        <v>108</v>
+      </c>
+      <c r="H101">
+        <v>365</v>
+      </c>
+      <c r="I101" t="s">
+        <v>156</v>
+      </c>
+      <c r="J101" t="s">
+        <v>157</v>
+      </c>
+      <c r="K101" t="s">
+        <v>158</v>
+      </c>
+      <c r="L101" t="s">
+        <v>159</v>
+      </c>
+      <c r="M101">
+        <v>0.02339300169489493</v>
+      </c>
+      <c r="N101">
+        <v>0.3361258776673434</v>
+      </c>
+      <c r="O101">
+        <v>-0.6354016128050141</v>
+      </c>
+      <c r="P101">
+        <v>0.6821876161948038</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>48</v>
+      </c>
+      <c r="R101">
+        <v>1.02366876406387</v>
+      </c>
+      <c r="S101">
+        <v>0.5297227021713093</v>
+      </c>
+      <c r="T101">
+        <v>1.978200545728484</v>
+      </c>
+      <c r="U101">
+        <v>0.06959595570932652</v>
+      </c>
+      <c r="V101">
+        <v>0.9445152560135034</v>
+      </c>
+      <c r="W101" t="s">
+        <v>49</v>
+      </c>
+      <c r="X101" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z101">
+        <v>598.6893345329158</v>
+      </c>
+      <c r="AA101">
+        <v>0.01167136924742329</v>
+      </c>
+      <c r="AD101">
+        <v>0.0005963141209567455</v>
+      </c>
+      <c r="AE101">
+        <v>0.4437640765909484</v>
+      </c>
+      <c r="AF101">
+        <v>0.0272874657852239</v>
+      </c>
+      <c r="AG101">
+        <v>0.2545027342663077</v>
+      </c>
+      <c r="AH101">
+        <v>0.3469882281035148</v>
+      </c>
+    </row>
+    <row r="102" spans="1:39">
+      <c r="A102" t="s">
+        <v>166</v>
+      </c>
+      <c r="B102" t="s">
+        <v>100</v>
+      </c>
+      <c r="C102" t="s">
+        <v>149</v>
+      </c>
+      <c r="D102" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+      <c r="F102" t="s">
+        <v>107</v>
+      </c>
+      <c r="G102" t="s">
+        <v>108</v>
+      </c>
+      <c r="H102">
+        <v>365</v>
+      </c>
+      <c r="I102" t="s">
+        <v>160</v>
+      </c>
+      <c r="J102" t="s">
+        <v>161</v>
+      </c>
+      <c r="K102" t="s">
+        <v>162</v>
+      </c>
+      <c r="L102" t="s">
+        <v>159</v>
+      </c>
+      <c r="M102">
+        <v>0.375905230575814</v>
+      </c>
+      <c r="N102">
+        <v>0.4403294238167053</v>
+      </c>
+      <c r="O102">
+        <v>-0.4871245814382016</v>
+      </c>
+      <c r="P102">
+        <v>1.23893504258983</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>48</v>
+      </c>
+      <c r="R102">
+        <v>1.456309113655008</v>
+      </c>
+      <c r="S102">
+        <v>0.6143904865261695</v>
+      </c>
+      <c r="T102">
+        <v>3.451935342466113</v>
+      </c>
+      <c r="U102">
+        <v>0.8536909192157257</v>
+      </c>
+      <c r="V102">
+        <v>0.3932762669267992</v>
+      </c>
+      <c r="W102" t="s">
+        <v>49</v>
+      </c>
+      <c r="X102" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z102">
+        <v>598.6893345329158</v>
+      </c>
+      <c r="AA102">
+        <v>0.01167136924742329</v>
+      </c>
+      <c r="AD102">
+        <v>0.0005963141209567455</v>
+      </c>
+      <c r="AE102">
+        <v>0.4437640765909484</v>
+      </c>
+      <c r="AF102">
+        <v>0.0272874657852239</v>
+      </c>
+      <c r="AG102">
+        <v>0.2545027342663077</v>
+      </c>
+      <c r="AH102">
+        <v>0.3469882281035148</v>
+      </c>
+    </row>
+    <row r="103" spans="1:39">
+      <c r="A103" t="s">
+        <v>166</v>
+      </c>
+      <c r="B103" t="s">
+        <v>100</v>
+      </c>
+      <c r="C103" t="s">
+        <v>149</v>
+      </c>
+      <c r="D103" t="s">
+        <v>41</v>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" t="s">
+        <v>107</v>
+      </c>
+      <c r="G103" t="s">
+        <v>108</v>
+      </c>
+      <c r="H103">
+        <v>365</v>
+      </c>
+      <c r="I103" t="s">
+        <v>163</v>
+      </c>
+      <c r="J103" t="s">
+        <v>164</v>
+      </c>
+      <c r="K103" t="s">
+        <v>165</v>
+      </c>
+      <c r="L103" t="s">
+        <v>159</v>
+      </c>
+      <c r="M103">
+        <v>1.461351208757332</v>
+      </c>
+      <c r="N103">
+        <v>0.6502888108778544</v>
+      </c>
+      <c r="O103">
+        <v>0.186808559887359</v>
+      </c>
+      <c r="P103">
+        <v>2.735893857627305</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>48</v>
+      </c>
+      <c r="R103">
+        <v>4.311781711175008</v>
+      </c>
+      <c r="S103">
+        <v>1.20539650171797</v>
+      </c>
+      <c r="T103">
+        <v>15.4235237105186</v>
+      </c>
+      <c r="U103">
+        <v>2.247234127840194</v>
+      </c>
+      <c r="V103">
+        <v>0.02462506818123131</v>
+      </c>
+      <c r="W103" t="s">
+        <v>49</v>
+      </c>
+      <c r="X103" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z103">
+        <v>598.6893345329158</v>
+      </c>
+      <c r="AA103">
+        <v>0.01167136924742329</v>
+      </c>
+      <c r="AD103">
+        <v>0.0005963141209567455</v>
+      </c>
+      <c r="AE103">
+        <v>0.4437640765909484</v>
+      </c>
+      <c r="AF103">
+        <v>0.0272874657852239</v>
+      </c>
+      <c r="AG103">
+        <v>0.2545027342663077</v>
+      </c>
+      <c r="AH103">
+        <v>0.3469882281035148</v>
+      </c>
+    </row>
+    <row r="104" spans="1:39">
+      <c r="A104" t="s">
+        <v>166</v>
+      </c>
+      <c r="B104" t="s">
+        <v>90</v>
+      </c>
+      <c r="C104" t="s">
+        <v>149</v>
+      </c>
+      <c r="D104" t="s">
+        <v>41</v>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
+        <v>107</v>
+      </c>
+      <c r="G104" t="s">
+        <v>108</v>
+      </c>
+      <c r="H104">
+        <v>365</v>
+      </c>
+      <c r="I104" t="s">
+        <v>91</v>
+      </c>
+      <c r="J104" t="s">
+        <v>92</v>
+      </c>
+      <c r="K104" t="s">
+        <v>93</v>
+      </c>
+      <c r="L104" t="s">
+        <v>94</v>
+      </c>
+      <c r="M104">
+        <v>0.03702360929177987</v>
+      </c>
+      <c r="N104">
+        <v>0.2142450110489068</v>
+      </c>
+      <c r="O104">
+        <v>-0.3828888962314632</v>
+      </c>
+      <c r="P104">
+        <v>0.456936114815023</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>48</v>
+      </c>
+      <c r="R104">
+        <v>1.037717520324671</v>
+      </c>
+      <c r="S104">
+        <v>0.6818886554768594</v>
+      </c>
+      <c r="T104">
+        <v>1.579227991754333</v>
+      </c>
+      <c r="U104">
+        <v>0.1728096682882773</v>
+      </c>
+      <c r="V104">
+        <v>0.8628010371884052</v>
+      </c>
+      <c r="Z104">
+        <v>598.6893345329158</v>
+      </c>
+      <c r="AA104">
+        <v>0.01167136924742329</v>
+      </c>
+      <c r="AD104">
+        <v>0.0005963141209567455</v>
+      </c>
+      <c r="AE104">
+        <v>0.4437640765909484</v>
+      </c>
+      <c r="AF104">
+        <v>0.0272874657852239</v>
+      </c>
+      <c r="AG104">
+        <v>0.2545027342663077</v>
+      </c>
+      <c r="AH104">
+        <v>0.3469882281035148</v>
+      </c>
+    </row>
+    <row r="105" spans="1:39">
+      <c r="A105" t="s">
+        <v>166</v>
+      </c>
+      <c r="B105" t="s">
+        <v>90</v>
+      </c>
+      <c r="C105" t="s">
+        <v>149</v>
+      </c>
+      <c r="D105" t="s">
+        <v>41</v>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+      <c r="F105" t="s">
+        <v>107</v>
+      </c>
+      <c r="G105" t="s">
+        <v>108</v>
+      </c>
+      <c r="H105">
+        <v>365</v>
+      </c>
+      <c r="I105" t="s">
+        <v>95</v>
+      </c>
+      <c r="J105" t="s">
+        <v>96</v>
+      </c>
+      <c r="K105" t="s">
+        <v>97</v>
+      </c>
+      <c r="L105" t="s">
+        <v>94</v>
+      </c>
+      <c r="M105">
+        <v>0.7978184222164202</v>
+      </c>
+      <c r="N105">
+        <v>0.6932058924998694</v>
+      </c>
+      <c r="O105">
+        <v>-0.5608401609542679</v>
+      </c>
+      <c r="P105">
+        <v>2.156477005387108</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>48</v>
+      </c>
+      <c r="R105">
+        <v>2.220691029985341</v>
+      </c>
+      <c r="S105">
+        <v>0.5707293578399918</v>
+      </c>
+      <c r="T105">
+        <v>8.640643034942544</v>
+      </c>
+      <c r="U105">
+        <v>1.150911195141883</v>
+      </c>
+      <c r="V105">
+        <v>0.2497687716340106</v>
+      </c>
+      <c r="Z105">
+        <v>598.6893345329158</v>
+      </c>
+      <c r="AA105">
+        <v>0.01167136924742329</v>
+      </c>
+      <c r="AD105">
+        <v>0.0005963141209567455</v>
+      </c>
+      <c r="AE105">
+        <v>0.4437640765909484</v>
+      </c>
+      <c r="AF105">
+        <v>0.0272874657852239</v>
+      </c>
+      <c r="AG105">
+        <v>0.2545027342663077</v>
+      </c>
+      <c r="AH105">
+        <v>0.3469882281035148</v>
+      </c>
+    </row>
+    <row r="106" spans="1:39">
+      <c r="A106" t="s">
+        <v>167</v>
+      </c>
+      <c r="B106" t="s">
+        <v>110</v>
+      </c>
+      <c r="C106" t="s">
+        <v>149</v>
+      </c>
+      <c r="D106" t="s">
+        <v>41</v>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" t="s">
+        <v>43</v>
+      </c>
+      <c r="H106">
+        <v>226</v>
+      </c>
+      <c r="I106" t="s">
+        <v>113</v>
+      </c>
+      <c r="J106" t="s">
+        <v>114</v>
+      </c>
+      <c r="K106" t="s">
+        <v>115</v>
+      </c>
+      <c r="L106" t="s">
+        <v>116</v>
+      </c>
+      <c r="M106">
+        <v>0.4204831929660624</v>
+      </c>
+      <c r="N106">
+        <v>0.1319708336146649</v>
+      </c>
+      <c r="O106">
+        <v>0.1618251120715914</v>
+      </c>
+      <c r="P106">
+        <v>0.6791412738605334</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>48</v>
+      </c>
+      <c r="R106">
+        <v>1.52269713443587</v>
+      </c>
+      <c r="S106">
+        <v>1.175654615540555</v>
+      </c>
+      <c r="T106">
+        <v>1.972183439396558</v>
+      </c>
+      <c r="U106">
+        <v>3.18618274545276</v>
+      </c>
+      <c r="V106">
+        <v>0.001441635039864584</v>
+      </c>
+      <c r="W106" t="s">
+        <v>49</v>
+      </c>
+      <c r="X106" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y106">
+        <v>1.847804844795774</v>
+      </c>
+      <c r="Z106">
+        <v>619.3403886128827</v>
+      </c>
+      <c r="AA106">
+        <v>0.02913853765991992</v>
+      </c>
+      <c r="AD106">
+        <v>-0.02104406814582626</v>
+      </c>
+      <c r="AE106">
+        <v>0.7130097650909896</v>
+      </c>
+      <c r="AF106">
+        <v>0.05664179320021405</v>
+      </c>
+      <c r="AG106">
+        <v>0.1908990300697498</v>
+      </c>
+      <c r="AH106">
+        <v>0.2595164925583584</v>
+      </c>
+    </row>
+    <row r="107" spans="1:39">
+      <c r="A107" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107" t="s">
+        <v>149</v>
+      </c>
+      <c r="D107" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" t="s">
+        <v>42</v>
+      </c>
+      <c r="G107" t="s">
+        <v>43</v>
+      </c>
+      <c r="H107">
+        <v>226</v>
+      </c>
+      <c r="I107" t="s">
+        <v>121</v>
+      </c>
+      <c r="J107" t="s">
+        <v>122</v>
+      </c>
+      <c r="K107" t="s">
+        <v>123</v>
+      </c>
+      <c r="L107" t="s">
+        <v>124</v>
+      </c>
+      <c r="M107">
+        <v>-0.1845274916284873</v>
+      </c>
+      <c r="N107">
+        <v>0.05349148703698052</v>
+      </c>
+      <c r="O107">
+        <v>-0.2893688797004603</v>
+      </c>
+      <c r="P107">
+        <v>-0.07968610355651437</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>48</v>
+      </c>
+      <c r="R107">
+        <v>0.8314970803763607</v>
+      </c>
+      <c r="S107">
+        <v>0.7487359609583156</v>
+      </c>
+      <c r="T107">
+        <v>0.9234061548072267</v>
+      </c>
+      <c r="U107">
+        <v>-3.449660905873061</v>
+      </c>
+      <c r="V107">
+        <v>0.0005612911158422043</v>
+      </c>
+      <c r="W107" t="s">
+        <v>68</v>
+      </c>
+      <c r="X107" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y107">
+        <v>1.847804844795774</v>
+      </c>
+      <c r="Z107">
+        <v>619.3403886128827</v>
+      </c>
+      <c r="AA107">
+        <v>0.02913853765991992</v>
+      </c>
+      <c r="AD107">
+        <v>-0.02104406814582626</v>
+      </c>
+      <c r="AE107">
+        <v>0.7130097650909896</v>
+      </c>
+      <c r="AF107">
+        <v>0.05664179320021405</v>
+      </c>
+      <c r="AG107">
+        <v>0.1908990300697498</v>
+      </c>
+      <c r="AH107">
+        <v>0.2595164925583584</v>
+      </c>
+    </row>
+    <row r="108" spans="1:39">
+      <c r="A108" t="s">
+        <v>168</v>
+      </c>
+      <c r="B108" t="s">
+        <v>110</v>
+      </c>
+      <c r="C108" t="s">
+        <v>149</v>
+      </c>
+      <c r="D108" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
+        <v>42</v>
+      </c>
+      <c r="G108" t="s">
+        <v>43</v>
+      </c>
+      <c r="H108">
+        <v>202</v>
+      </c>
+      <c r="I108" t="s">
+        <v>113</v>
+      </c>
+      <c r="J108" t="s">
+        <v>114</v>
+      </c>
+      <c r="K108" t="s">
+        <v>115</v>
+      </c>
+      <c r="L108" t="s">
+        <v>116</v>
+      </c>
+      <c r="M108">
+        <v>0.4140782800973458</v>
+      </c>
+      <c r="N108">
+        <v>0.1321062908742811</v>
+      </c>
+      <c r="O108">
+        <v>0.1551547078525826</v>
+      </c>
+      <c r="P108">
+        <v>0.673001852342109</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>48</v>
+      </c>
+      <c r="R108">
+        <v>1.512975558122901</v>
+      </c>
+      <c r="S108">
+        <v>1.167838620935225</v>
+      </c>
+      <c r="T108">
+        <v>1.960112466261954</v>
+      </c>
+      <c r="U108">
+        <v>3.134432715936316</v>
+      </c>
+      <c r="V108">
+        <v>0.001721867365777989</v>
+      </c>
+      <c r="W108" t="s">
+        <v>49</v>
+      </c>
+      <c r="X108" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y108">
+        <v>2.055689691353061</v>
+      </c>
+      <c r="Z108">
+        <v>583.4274508460501</v>
+      </c>
+      <c r="AA108">
+        <v>0.0268258891904074</v>
+      </c>
+      <c r="AD108">
+        <v>-0.04440392055852355</v>
+      </c>
+      <c r="AE108">
+        <v>0.8971384949822991</v>
+      </c>
+      <c r="AF108">
+        <v>0.03803659139362264</v>
+      </c>
+      <c r="AG108">
+        <v>0.2753145220809197</v>
+      </c>
+      <c r="AH108">
+        <v>0.4702112881795306</v>
+      </c>
+    </row>
+    <row r="109" spans="1:39">
+      <c r="A109" t="s">
+        <v>168</v>
+      </c>
+      <c r="B109" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" t="s">
+        <v>149</v>
+      </c>
+      <c r="D109" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" t="s">
+        <v>42</v>
+      </c>
+      <c r="G109" t="s">
+        <v>43</v>
+      </c>
+      <c r="H109">
+        <v>202</v>
+      </c>
+      <c r="I109" t="s">
+        <v>121</v>
+      </c>
+      <c r="J109" t="s">
+        <v>122</v>
+      </c>
+      <c r="K109" t="s">
+        <v>123</v>
+      </c>
+      <c r="L109" t="s">
+        <v>124</v>
+      </c>
+      <c r="M109">
+        <v>-0.1659273085960489</v>
+      </c>
+      <c r="N109">
+        <v>0.05353266861820654</v>
+      </c>
+      <c r="O109">
+        <v>-0.2708494110840513</v>
+      </c>
+      <c r="P109">
+        <v>-0.06100520610804655</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>48</v>
+      </c>
+      <c r="R109">
+        <v>0.8471078094073418</v>
+      </c>
+      <c r="S109">
+        <v>0.7627313466439131</v>
+      </c>
+      <c r="T109">
+        <v>0.9408183417613205</v>
+      </c>
+      <c r="U109">
+        <v>-3.099552345866367</v>
+      </c>
+      <c r="V109">
+        <v>0.00193813326680686</v>
+      </c>
+      <c r="W109" t="s">
+        <v>68</v>
+      </c>
+      <c r="X109" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y109">
+        <v>2.055689691353061</v>
+      </c>
+      <c r="Z109">
+        <v>583.4274508460501</v>
+      </c>
+      <c r="AA109">
+        <v>0.0268258891904074</v>
+      </c>
+      <c r="AD109">
+        <v>-0.04440392055852355</v>
+      </c>
+      <c r="AE109">
+        <v>0.8971384949822991</v>
+      </c>
+      <c r="AF109">
+        <v>0.03803659139362264</v>
+      </c>
+      <c r="AG109">
+        <v>0.2753145220809197</v>
+      </c>
+      <c r="AH109">
+        <v>0.4702112881795306</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
